--- a/src/attributions/attributions_saliency_traj_446.xlsx
+++ b/src/attributions/attributions_saliency_traj_446.xlsx
@@ -1568,571 +1568,571 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>9.7988424840878e-07</v>
+        <v>5.435211278381757e-06</v>
       </c>
       <c r="B3" t="n">
-        <v>2.727936043811496e-05</v>
+        <v>6.670711445622146e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.111401815023783e-07</v>
+        <v>1.314836481469683e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.717922714306042e-05</v>
+        <v>3.98967313230969e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>6.023764399287757e-06</v>
+        <v>2.324309025425464e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.41749933391111e-06</v>
+        <v>2.144511745427735e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>2.518055680411635e-06</v>
+        <v>7.700819878664333e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>2.146274937331327e-06</v>
+        <v>2.124488901245059e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>2.471265929671063e-07</v>
+        <v>3.276221377745969e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>4.112055648874957e-06</v>
+        <v>1.321806030318839e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>2.139191565220244e-05</v>
+        <v>7.012046262389049e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.17665308607684e-06</v>
+        <v>1.98228626686614e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>1.172703741758596e-05</v>
+        <v>5.454313941299915e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>6.917386144777993e-06</v>
+        <v>3.260567973484285e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>4.844701834372245e-06</v>
+        <v>1.117658575822134e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>2.017034603341017e-06</v>
+        <v>4.621156222128775e-07</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.336249730840791e-06</v>
+        <v>1.628826794330962e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>7.899251386334072e-08</v>
+        <v>3.072846084251069e-07</v>
       </c>
       <c r="S3" t="n">
-        <v>1.202927023769007e-06</v>
+        <v>2.438286173855886e-06</v>
       </c>
       <c r="T3" t="n">
-        <v>4.370926035335287e-06</v>
+        <v>7.672143510717433e-06</v>
       </c>
       <c r="U3" t="n">
-        <v>3.747182972801966e-07</v>
+        <v>3.19778064294951e-06</v>
       </c>
       <c r="V3" t="n">
-        <v>3.411248826523661e-06</v>
+        <v>7.335294753829658e-07</v>
       </c>
       <c r="W3" t="n">
-        <v>1.44510090649419e-06</v>
+        <v>6.090632496125181e-07</v>
       </c>
       <c r="X3" t="n">
-        <v>1.93111054613837e-06</v>
+        <v>1.594814057170879e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.791350882740517e-06</v>
+        <v>5.979798061162001e-07</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.576731387511245e-06</v>
+        <v>1.190778675663751e-06</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.228260311516351e-06</v>
+        <v>8.712357157492079e-06</v>
       </c>
       <c r="AB3" t="n">
-        <v>9.620678156352369e-07</v>
+        <v>6.180659966048552e-06</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.54343353844888e-06</v>
+        <v>1.323646756645758e-06</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.009335733215266e-06</v>
+        <v>1.905235194499255e-06</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.170490688513382e-06</v>
+        <v>9.195508027914912e-06</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.26748591355863e-06</v>
+        <v>3.379390591362608e-06</v>
       </c>
       <c r="AG3" t="n">
-        <v>6.077596026443643e-07</v>
+        <v>3.554320073817507e-06</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.498638766861404e-06</v>
+        <v>5.114950909046456e-06</v>
       </c>
       <c r="AI3" t="n">
-        <v>6.156445806482225e-07</v>
+        <v>3.019253426828072e-06</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.650223794058547e-06</v>
+        <v>3.670098067232175e-06</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.724051799101289e-06</v>
+        <v>5.359727310860762e-07</v>
       </c>
       <c r="AL3" t="n">
-        <v>4.673025159718236e-06</v>
+        <v>1.611290826986078e-05</v>
       </c>
       <c r="AM3" t="n">
-        <v>5.105497962176742e-07</v>
+        <v>4.903572516923305e-07</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.375158149130584e-06</v>
+        <v>6.601655059057521e-06</v>
       </c>
       <c r="AO3" t="n">
-        <v>7.710361273893795e-07</v>
+        <v>1.691518991719931e-05</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.26459235616494e-06</v>
+        <v>1.071392307494534e-05</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.144624661719718e-06</v>
+        <v>2.056283619822352e-06</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.549851276649861e-06</v>
+        <v>1.261222564608033e-06</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.695484343144926e-06</v>
+        <v>1.937910838023527e-06</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.964432613021927e-06</v>
+        <v>4.70502754978952e-06</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.811795846151654e-05</v>
+        <v>4.816802538698539e-05</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.361385898235312e-06</v>
+        <v>1.231236410603742e-06</v>
       </c>
       <c r="AW3" t="n">
-        <v>6.083508196752518e-06</v>
+        <v>1.358401550533017e-05</v>
       </c>
       <c r="AX3" t="n">
-        <v>2.96382381748117e-07</v>
+        <v>6.141354788269382e-06</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.348600221717788e-06</v>
+        <v>3.790720938923187e-06</v>
       </c>
       <c r="AZ3" t="n">
-        <v>2.5673875825305e-07</v>
+        <v>2.508672650947119e-06</v>
       </c>
       <c r="BA3" t="n">
-        <v>4.124074166611535e-06</v>
+        <v>2.145514599760645e-06</v>
       </c>
       <c r="BB3" t="n">
-        <v>2.204257498306106e-06</v>
+        <v>2.828355036399444e-06</v>
       </c>
       <c r="BC3" t="n">
-        <v>5.557240001508035e-08</v>
+        <v>8.621964298072271e-06</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.441941655386472e-06</v>
+        <v>9.968646281777183e-07</v>
       </c>
       <c r="BE3" t="n">
-        <v>3.404068138479488e-06</v>
+        <v>1.336537934548687e-05</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.958244976980495e-06</v>
+        <v>6.688487246719887e-06</v>
       </c>
       <c r="BG3" t="n">
-        <v>7.825922693882603e-06</v>
+        <v>8.271151273220312e-06</v>
       </c>
       <c r="BH3" t="n">
-        <v>5.557410531764617e-09</v>
+        <v>1.523463470221031e-05</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.431425630471495e-06</v>
+        <v>3.228685727663105e-07</v>
       </c>
       <c r="BJ3" t="n">
-        <v>4.516523858910659e-06</v>
+        <v>5.343061729945475e-06</v>
       </c>
       <c r="BK3" t="n">
-        <v>3.546542188814783e-07</v>
+        <v>7.356832156801829e-06</v>
       </c>
       <c r="BL3" t="n">
-        <v>3.08682342620159e-06</v>
+        <v>1.047337718773633e-06</v>
       </c>
       <c r="BM3" t="n">
-        <v>2.616831125124008e-06</v>
+        <v>8.792749213171192e-06</v>
       </c>
       <c r="BN3" t="n">
-        <v>2.011020114878193e-06</v>
+        <v>1.515684971309383e-06</v>
       </c>
       <c r="BO3" t="n">
-        <v>2.522953650441195e-07</v>
+        <v>4.785630608239444e-06</v>
       </c>
       <c r="BP3" t="n">
-        <v>3.620118377511972e-06</v>
+        <v>8.886086106940638e-06</v>
       </c>
       <c r="BQ3" t="n">
-        <v>3.070714228670113e-06</v>
+        <v>3.591158019844443e-06</v>
       </c>
       <c r="BR3" t="n">
-        <v>1.514731025054061e-06</v>
+        <v>8.744744263822213e-06</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.785907670637243e-06</v>
+        <v>3.946427113987738e-06</v>
       </c>
       <c r="BT3" t="n">
-        <v>1.244257646249025e-06</v>
+        <v>6.394326419467689e-07</v>
       </c>
       <c r="BU3" t="n">
-        <v>2.508423676772509e-06</v>
+        <v>5.632185093418229e-06</v>
       </c>
       <c r="BV3" t="n">
-        <v>9.665334800956771e-06</v>
+        <v>3.702117828652263e-05</v>
       </c>
       <c r="BW3" t="n">
-        <v>2.108500211761566e-06</v>
+        <v>5.698409950127825e-06</v>
       </c>
       <c r="BX3" t="n">
-        <v>3.426830289754434e-06</v>
+        <v>1.281944696529536e-05</v>
       </c>
       <c r="BY3" t="n">
-        <v>2.299580501130549e-06</v>
+        <v>4.903096396446927e-06</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1.607947979209712e-06</v>
+        <v>1.106567196984543e-05</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.44382352118555e-06</v>
+        <v>7.932316634651215e-07</v>
       </c>
       <c r="CB3" t="n">
-        <v>7.655921763216611e-08</v>
+        <v>1.46727211358666e-06</v>
       </c>
       <c r="CC3" t="n">
-        <v>2.374053565290524e-06</v>
+        <v>5.527135726879351e-06</v>
       </c>
       <c r="CD3" t="n">
-        <v>6.85348936713126e-07</v>
+        <v>4.33054594850546e-07</v>
       </c>
       <c r="CE3" t="n">
-        <v>3.677592076201108e-06</v>
+        <v>1.904012606246397e-05</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.233660325146047e-06</v>
+        <v>3.989232936874032e-06</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.432277597108623e-06</v>
+        <v>1.00917968666181e-05</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.163140154858411e-06</v>
+        <v>1.238802838088304e-06</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.19220726446656e-06</v>
+        <v>5.514768872671993e-07</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.175256556962267e-06</v>
+        <v>1.228656174134812e-06</v>
       </c>
       <c r="CK3" t="n">
-        <v>4.62521768440638e-07</v>
+        <v>2.261412390680562e-08</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.425327582182945e-06</v>
+        <v>1.065105493580631e-06</v>
       </c>
       <c r="CM3" t="n">
-        <v>5.073029115010286e-06</v>
+        <v>8.838165740598924e-06</v>
       </c>
       <c r="CN3" t="n">
-        <v>8.579997370361525e-07</v>
+        <v>2.237032276752871e-05</v>
       </c>
       <c r="CO3" t="n">
-        <v>3.204429788183916e-07</v>
+        <v>1.148021874541882e-05</v>
       </c>
       <c r="CP3" t="n">
-        <v>2.751040938164806e-06</v>
+        <v>1.057634744938696e-05</v>
       </c>
       <c r="CQ3" t="n">
-        <v>4.183114015177125e-06</v>
+        <v>1.285475900658639e-05</v>
       </c>
       <c r="CR3" t="n">
-        <v>2.136931243512663e-06</v>
+        <v>3.005962753377389e-06</v>
       </c>
       <c r="CS3" t="n">
-        <v>4.752615041070385e-06</v>
+        <v>5.172065357328393e-06</v>
       </c>
       <c r="CT3" t="n">
-        <v>2.66689721684088e-06</v>
+        <v>1.153874222836748e-06</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.589050953043625e-06</v>
+        <v>4.384070507512661e-06</v>
       </c>
       <c r="CV3" t="n">
-        <v>7.200056302281155e-07</v>
+        <v>3.182372893206775e-06</v>
       </c>
       <c r="CW3" t="n">
-        <v>3.507536803226685e-06</v>
+        <v>1.897409310913645e-05</v>
       </c>
       <c r="CX3" t="n">
-        <v>2.495986109352089e-06</v>
+        <v>3.408735210541636e-06</v>
       </c>
       <c r="CY3" t="n">
-        <v>3.364158374097315e-06</v>
+        <v>9.637273251428269e-06</v>
       </c>
       <c r="CZ3" t="n">
-        <v>7.671765729355684e-07</v>
+        <v>3.968433702539187e-06</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.585305199114373e-06</v>
+        <v>1.441842186977738e-06</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.274726969313633e-06</v>
+        <v>8.400832030019956e-07</v>
       </c>
       <c r="DC3" t="n">
-        <v>9.334690957985003e-07</v>
+        <v>1.335915158051648e-06</v>
       </c>
       <c r="DD3" t="n">
-        <v>9.267396308132447e-07</v>
+        <v>2.576488441263791e-06</v>
       </c>
       <c r="DE3" t="n">
-        <v>1.90075411410362e-06</v>
+        <v>1.242128109879559e-05</v>
       </c>
       <c r="DF3" t="n">
-        <v>4.471344254852738e-06</v>
+        <v>1.808653905754909e-05</v>
       </c>
       <c r="DG3" t="n">
-        <v>8.816891750029754e-08</v>
+        <v>5.720299668610096e-06</v>
       </c>
       <c r="DH3" t="n">
-        <v>1.448869443265721e-05</v>
+        <v>8.854019142745528e-06</v>
       </c>
       <c r="DI3" t="n">
-        <v>2.916778839789913e-06</v>
+        <v>1.527544372947887e-05</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.196289531435468e-06</v>
+        <v>1.718002931738738e-05</v>
       </c>
       <c r="DK3" t="n">
-        <v>3.278947588114534e-06</v>
+        <v>1.730150870571379e-06</v>
       </c>
       <c r="DL3" t="n">
-        <v>2.605576128189568e-07</v>
+        <v>1.702523150015622e-05</v>
       </c>
       <c r="DM3" t="n">
-        <v>7.078407548988253e-08</v>
+        <v>1.659281679167179e-06</v>
       </c>
       <c r="DN3" t="n">
-        <v>1.349465946987038e-06</v>
+        <v>2.232949555036612e-06</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.754609113253537e-06</v>
+        <v>1.61144052981399e-05</v>
       </c>
       <c r="DP3" t="n">
-        <v>1.591568889125483e-06</v>
+        <v>4.793407697434304e-07</v>
       </c>
       <c r="DQ3" t="n">
-        <v>1.170610516965098e-06</v>
+        <v>8.304463335662149e-06</v>
       </c>
       <c r="DR3" t="n">
-        <v>1.077030333362927e-06</v>
+        <v>1.855137270467822e-07</v>
       </c>
       <c r="DS3" t="n">
-        <v>1.29053182718053e-06</v>
+        <v>2.057097617580439e-06</v>
       </c>
       <c r="DT3" t="n">
-        <v>1.320532874160563e-06</v>
+        <v>2.20498031922034e-06</v>
       </c>
       <c r="DU3" t="n">
-        <v>2.720856286941853e-07</v>
+        <v>5.590403816313483e-06</v>
       </c>
       <c r="DV3" t="n">
-        <v>2.591852307887166e-06</v>
+        <v>1.284049176319968e-05</v>
       </c>
       <c r="DW3" t="n">
-        <v>5.450445428323292e-08</v>
+        <v>1.144176167144906e-07</v>
       </c>
       <c r="DX3" t="n">
-        <v>2.534210352678201e-06</v>
+        <v>1.390403667755891e-06</v>
       </c>
       <c r="DY3" t="n">
-        <v>2.054121750916238e-06</v>
+        <v>1.407063450642454e-06</v>
       </c>
       <c r="DZ3" t="n">
-        <v>1.594200625731901e-06</v>
+        <v>1.24869475257583e-05</v>
       </c>
       <c r="EA3" t="n">
-        <v>2.242102254967904e-06</v>
+        <v>1.699435870250454e-06</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.516952806923655e-06</v>
+        <v>1.052143488777801e-05</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.356368443339306e-06</v>
+        <v>6.492609827546403e-07</v>
       </c>
       <c r="ED3" t="n">
-        <v>4.382907832223282e-07</v>
+        <v>1.466683534090407e-05</v>
       </c>
       <c r="EE3" t="n">
-        <v>1.087251234821451e-06</v>
+        <v>1.082587004930247e-05</v>
       </c>
       <c r="EF3" t="n">
-        <v>2.128431333403569e-06</v>
+        <v>8.534530024917331e-07</v>
       </c>
       <c r="EG3" t="n">
-        <v>3.301774086139631e-06</v>
+        <v>1.324741879216162e-05</v>
       </c>
       <c r="EH3" t="n">
-        <v>2.214835376435076e-06</v>
+        <v>2.966568899864797e-06</v>
       </c>
       <c r="EI3" t="n">
-        <v>1.882920741991256e-06</v>
+        <v>5.970925030851504e-06</v>
       </c>
       <c r="EJ3" t="n">
-        <v>6.012805897626095e-07</v>
+        <v>6.726988885930041e-06</v>
       </c>
       <c r="EK3" t="n">
-        <v>1.112809968617512e-06</v>
+        <v>2.598779360596382e-07</v>
       </c>
       <c r="EL3" t="n">
-        <v>6.550231432811415e-07</v>
+        <v>1.803129975996853e-06</v>
       </c>
       <c r="EM3" t="n">
-        <v>4.450266430922056e-07</v>
+        <v>1.373694090034405e-06</v>
       </c>
       <c r="EN3" t="n">
-        <v>6.778255396966415e-07</v>
+        <v>8.565495477341756e-07</v>
       </c>
       <c r="EO3" t="n">
-        <v>1.006577804218978e-06</v>
+        <v>2.087749635393266e-06</v>
       </c>
       <c r="EP3" t="n">
-        <v>3.420704160816967e-06</v>
+        <v>9.29127236304339e-06</v>
       </c>
       <c r="EQ3" t="n">
-        <v>3.262018935856759e-06</v>
+        <v>5.579277967626695e-06</v>
       </c>
       <c r="ER3" t="n">
-        <v>2.205917098763166e-06</v>
+        <v>3.010845603057533e-06</v>
       </c>
       <c r="ES3" t="n">
-        <v>2.555232413214981e-06</v>
+        <v>4.240415819367627e-06</v>
       </c>
       <c r="ET3" t="n">
-        <v>2.340106675546849e-06</v>
+        <v>9.076586138689891e-06</v>
       </c>
       <c r="EU3" t="n">
-        <v>1.718220573820872e-06</v>
+        <v>4.481257747102063e-06</v>
       </c>
       <c r="EV3" t="n">
-        <v>3.611987722251797e-06</v>
+        <v>1.186967665489647e-06</v>
       </c>
       <c r="EW3" t="n">
-        <v>8.173087735485751e-07</v>
+        <v>5.305936156219104e-06</v>
       </c>
       <c r="EX3" t="n">
-        <v>2.744791913755762e-07</v>
+        <v>6.543959898408502e-07</v>
       </c>
       <c r="EY3" t="n">
-        <v>4.021582753921393e-06</v>
+        <v>2.141445293091238e-05</v>
       </c>
       <c r="EZ3" t="n">
-        <v>2.036957766904379e-06</v>
+        <v>2.194257831433788e-06</v>
       </c>
       <c r="FA3" t="n">
-        <v>2.714637048484292e-06</v>
+        <v>1.15395578177413e-05</v>
       </c>
       <c r="FB3" t="n">
-        <v>6.954629725441919e-07</v>
+        <v>1.196043058371288e-06</v>
       </c>
       <c r="FC3" t="n">
-        <v>1.748983777360991e-06</v>
+        <v>2.738550165304332e-06</v>
       </c>
       <c r="FD3" t="n">
-        <v>1.69850648035208e-06</v>
+        <v>2.022613898589043e-06</v>
       </c>
       <c r="FE3" t="n">
-        <v>6.877293117213412e-07</v>
+        <v>1.800816562536056e-06</v>
       </c>
       <c r="FF3" t="n">
-        <v>1.486950282014732e-06</v>
+        <v>2.056188122878666e-06</v>
       </c>
       <c r="FG3" t="n">
-        <v>4.944522515870631e-07</v>
+        <v>4.430173248692881e-06</v>
       </c>
       <c r="FH3" t="n">
-        <v>3.221633050998207e-06</v>
+        <v>1.245298244612059e-05</v>
       </c>
       <c r="FI3" t="n">
-        <v>2.419829797872808e-06</v>
+        <v>6.306221166596515e-06</v>
       </c>
       <c r="FJ3" t="n">
-        <v>3.244244453526335e-06</v>
+        <v>2.714060656217043e-06</v>
       </c>
       <c r="FK3" t="n">
-        <v>1.4105499985817e-06</v>
+        <v>1.853853746069944e-07</v>
       </c>
       <c r="FL3" t="n">
-        <v>6.894462103446131e-07</v>
+        <v>3.217703579139197e-06</v>
       </c>
       <c r="FM3" t="n">
-        <v>1.366816832160112e-06</v>
+        <v>2.237244643765735e-06</v>
       </c>
       <c r="FN3" t="n">
-        <v>1.637907303120301e-06</v>
+        <v>2.763237944236607e-06</v>
       </c>
       <c r="FO3" t="n">
-        <v>2.000729892870368e-07</v>
+        <v>6.42701752440189e-06</v>
       </c>
       <c r="FP3" t="n">
-        <v>9.794923698791536e-07</v>
+        <v>2.069475840471569e-06</v>
       </c>
       <c r="FQ3" t="n">
-        <v>3.538837972882902e-06</v>
+        <v>1.607708691153675e-05</v>
       </c>
       <c r="FR3" t="n">
-        <v>7.695322892686818e-06</v>
+        <v>2.610695446492173e-07</v>
       </c>
       <c r="FS3" t="n">
-        <v>4.566121560856118e-07</v>
+        <v>2.427204526611604e-05</v>
       </c>
       <c r="FT3" t="n">
-        <v>6.73373961035395e-07</v>
+        <v>1.395775325363502e-05</v>
       </c>
       <c r="FU3" t="n">
-        <v>1.570365810721341e-07</v>
+        <v>1.37368488140055e-06</v>
       </c>
       <c r="FV3" t="n">
-        <v>1.478698777646059e-06</v>
+        <v>1.682736296970688e-06</v>
       </c>
       <c r="FW3" t="n">
-        <v>3.632538209785707e-06</v>
+        <v>4.178386461717309e-06</v>
       </c>
       <c r="FX3" t="n">
-        <v>2.21452728510485e-06</v>
+        <v>1.616239023860544e-05</v>
       </c>
       <c r="FY3" t="n">
-        <v>3.327045760670444e-06</v>
+        <v>2.084440438920865e-06</v>
       </c>
       <c r="FZ3" t="n">
-        <v>1.153582331880898e-07</v>
+        <v>1.563900514156558e-05</v>
       </c>
       <c r="GA3" t="n">
-        <v>1.337841695203679e-06</v>
+        <v>5.28740974914399e-06</v>
       </c>
       <c r="GB3" t="n">
-        <v>1.481786853219091e-07</v>
+        <v>6.070572453609202e-06</v>
       </c>
       <c r="GC3" t="n">
-        <v>1.448483317290084e-06</v>
+        <v>2.054557262454182e-05</v>
       </c>
       <c r="GD3" t="n">
-        <v>1.745035206113243e-06</v>
+        <v>9.707212484499905e-06</v>
       </c>
       <c r="GE3" t="n">
-        <v>8.880011591827497e-06</v>
+        <v>1.461036026739748e-05</v>
       </c>
       <c r="GF3" t="n">
-        <v>2.04201887754607e-06</v>
+        <v>4.215253738948377e-06</v>
       </c>
       <c r="GG3" t="n">
-        <v>2.744757239270257e-06</v>
+        <v>2.11916722037131e-06</v>
       </c>
     </row>
     <row r="4">
@@ -2706,5123 +2706,5123 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.0003427093906793743</v>
+        <v>0.1109615713357925</v>
       </c>
       <c r="B5" t="n">
-        <v>0.007074887864291668</v>
+        <v>0.3669139742851257</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0003954570274800062</v>
+        <v>0.001538567245006561</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003062558360397816</v>
+        <v>0.1800787448883057</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0006815736996941268</v>
+        <v>0.1744547784328461</v>
       </c>
       <c r="F5" t="n">
-        <v>6.989850953686982e-05</v>
+        <v>0.08318288624286652</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0006616997998207808</v>
+        <v>0.121550664305687</v>
       </c>
       <c r="H5" t="n">
-        <v>0.001766788889653981</v>
+        <v>0.05419312790036201</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0002068929316010326</v>
+        <v>0.003512251190841198</v>
       </c>
       <c r="J5" t="n">
-        <v>7.874041330069304e-06</v>
+        <v>0.07825544476509094</v>
       </c>
       <c r="K5" t="n">
-        <v>0.006233584135770798</v>
+        <v>0.4638679027557373</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0003591147251427174</v>
+        <v>0.01340414583683014</v>
       </c>
       <c r="M5" t="n">
-        <v>0.003347890451550484</v>
+        <v>0.2640771865844727</v>
       </c>
       <c r="N5" t="n">
-        <v>0.001188888330943882</v>
+        <v>0.232093870639801</v>
       </c>
       <c r="O5" t="n">
-        <v>0.00119878095574677</v>
+        <v>0.04694750159978867</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0003172311699017882</v>
+        <v>0.09652276337146759</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0003603850200306624</v>
+        <v>0.08943891525268555</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0005201284657232463</v>
+        <v>0.01065056584775448</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0002704951330088079</v>
+        <v>0.01457473356276751</v>
       </c>
       <c r="T5" t="n">
-        <v>0.00143978965934366</v>
+        <v>0.04938540235161781</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0005672075785696507</v>
+        <v>0.04818979650735855</v>
       </c>
       <c r="V5" t="n">
-        <v>2.078104444080964e-05</v>
+        <v>0.02174863964319229</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0009545037755742669</v>
+        <v>0.003923358861356974</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0009902119636535645</v>
+        <v>0.05208474025130272</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0003211184230167419</v>
+        <v>0.01474028173834085</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.0004827150260098279</v>
+        <v>0.04298032447695732</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0005246052169241011</v>
+        <v>0.03882195055484772</v>
       </c>
       <c r="AB5" t="n">
-        <v>8.651596726849675e-05</v>
+        <v>0.038141880184412</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.001473412732593715</v>
+        <v>0.004475520923733711</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.0002452727640047669</v>
+        <v>0.01459784805774689</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.0005592519300989807</v>
+        <v>0.09276033192873001</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.000391271838452667</v>
+        <v>0.04157070070505142</v>
       </c>
       <c r="AG5" t="n">
-        <v>8.336280006915331e-05</v>
+        <v>0.03841760754585266</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.0009903388563543558</v>
+        <v>0.01157777849584818</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.0003380324633326381</v>
+        <v>0.09441413730382919</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.0001918696652865037</v>
+        <v>0.002573540434241295</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.0003272672765888274</v>
+        <v>0.007032787427306175</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.0005114821251481771</v>
+        <v>0.1145453304052353</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.957987296918873e-05</v>
+        <v>0.04876543208956718</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.0009086871286854148</v>
+        <v>0.03184271603822708</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.0007442425703629851</v>
+        <v>0.09229427576065063</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.0004388417582958937</v>
+        <v>0.01447831187397242</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.0005314472364261746</v>
+        <v>0.001730700954794884</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.0005828000139445066</v>
+        <v>0.06534294039011002</v>
       </c>
       <c r="AS5" t="n">
-        <v>7.911150896688923e-05</v>
+        <v>0.01859994791448116</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.0003119392204098403</v>
+        <v>0.01545341312885284</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.004266898613423109</v>
+        <v>0.3318633437156677</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.001104990253224969</v>
+        <v>0.07892529666423798</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.0006919075967743993</v>
+        <v>0.0815102830529213</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.001769423368386924</v>
+        <v>0.1345766633749008</v>
       </c>
       <c r="AY5" t="n">
-        <v>0.0005655373097397387</v>
+        <v>0.05043903365731239</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.0003585458325687796</v>
+        <v>0.01848267950117588</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.001560427015647292</v>
+        <v>0.006347432732582092</v>
       </c>
       <c r="BB5" t="n">
-        <v>8.071136107901111e-05</v>
+        <v>0.02651568688452244</v>
       </c>
       <c r="BC5" t="n">
-        <v>0.001142856432124972</v>
+        <v>0.0997626930475235</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.0009657817427068949</v>
+        <v>0.01314463000744581</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.001322963275015354</v>
+        <v>0.1005102396011353</v>
       </c>
       <c r="BF5" t="n">
-        <v>0.0002998292620759457</v>
+        <v>0.03277577832341194</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.001641292008571327</v>
+        <v>0.07206981629133224</v>
       </c>
       <c r="BH5" t="n">
-        <v>0.0001561049866722897</v>
+        <v>0.03307739645242691</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.0003087558434344828</v>
+        <v>0.00489148311316967</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.0005684511852450669</v>
+        <v>0.0009930483065545559</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.000288062758045271</v>
+        <v>0.04202352836728096</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.0008188639767467976</v>
+        <v>0.0005242442712187767</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.0003480961022432894</v>
+        <v>0.008674321696162224</v>
       </c>
       <c r="BN5" t="n">
-        <v>0.0002921929990407079</v>
+        <v>0.0487414114177227</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.001276425085961819</v>
+        <v>0.005130931735038757</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.001613273750990629</v>
+        <v>0.02905658818781376</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.0009361824486404657</v>
+        <v>0.005398205015808344</v>
       </c>
       <c r="BR5" t="n">
-        <v>0.0003353176871314645</v>
+        <v>0.09713277965784073</v>
       </c>
       <c r="BS5" t="n">
-        <v>0.0001332197716692463</v>
+        <v>0.02489763870835304</v>
       </c>
       <c r="BT5" t="n">
-        <v>0.001249239547178149</v>
+        <v>0.005733206402510405</v>
       </c>
       <c r="BU5" t="n">
-        <v>0.0001462493964936584</v>
+        <v>0.03563118353486061</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.00256863865070045</v>
+        <v>0.2554161250591278</v>
       </c>
       <c r="BW5" t="n">
-        <v>0.0002419712109258398</v>
+        <v>0.0162869393825531</v>
       </c>
       <c r="BX5" t="n">
-        <v>1.98741108761169e-05</v>
+        <v>0.09531044960021973</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.001160756801255047</v>
+        <v>0.04555460065603256</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0.0003212394658476114</v>
+        <v>0.06410815566778183</v>
       </c>
       <c r="CA5" t="n">
-        <v>0.0004677808610722423</v>
+        <v>0.03964085131883621</v>
       </c>
       <c r="CB5" t="n">
-        <v>0.0002428197039989755</v>
+        <v>0.01267708837985992</v>
       </c>
       <c r="CC5" t="n">
-        <v>0.0001225379382958636</v>
+        <v>0.01510061696171761</v>
       </c>
       <c r="CD5" t="n">
-        <v>0.0001452876749681309</v>
+        <v>0.01916037686169147</v>
       </c>
       <c r="CE5" t="n">
-        <v>0.001429999014362693</v>
+        <v>0.1246620863676071</v>
       </c>
       <c r="CF5" t="n">
-        <v>0.0001050574137479998</v>
+        <v>0.0150517039000988</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.0001829326502047479</v>
+        <v>0.05460336804389954</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.0001965127885341644</v>
+        <v>0.02163275144994259</v>
       </c>
       <c r="CI5" t="n">
-        <v>7.565093983430415e-05</v>
+        <v>0.005484903231263161</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0.0002579463180154562</v>
+        <v>0.01901426538825035</v>
       </c>
       <c r="CK5" t="n">
-        <v>6.748789746779948e-05</v>
+        <v>0.01062546111643314</v>
       </c>
       <c r="CL5" t="n">
-        <v>8.182789315469563e-06</v>
+        <v>0.01129750348627567</v>
       </c>
       <c r="CM5" t="n">
-        <v>0.001334457658231258</v>
+        <v>0.05441568791866302</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.0007321013836190104</v>
+        <v>0.2546215951442719</v>
       </c>
       <c r="CO5" t="n">
-        <v>9.384623263031244e-05</v>
+        <v>0.0648774579167366</v>
       </c>
       <c r="CP5" t="n">
-        <v>0.002017260063439608</v>
+        <v>0.1234624087810516</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.001993297366425395</v>
+        <v>0.01523406989872456</v>
       </c>
       <c r="CR5" t="n">
-        <v>0.001891531865112484</v>
+        <v>0.03235328570008278</v>
       </c>
       <c r="CS5" t="n">
-        <v>0.0008209377992898226</v>
+        <v>0.06808525323867798</v>
       </c>
       <c r="CT5" t="n">
-        <v>0.000917098019272089</v>
+        <v>0.0006477050483226776</v>
       </c>
       <c r="CU5" t="n">
-        <v>0.0002473218482919037</v>
+        <v>0.0251275822520256</v>
       </c>
       <c r="CV5" t="n">
-        <v>0.0001956716005224735</v>
+        <v>0.003500614780932665</v>
       </c>
       <c r="CW5" t="n">
-        <v>0.001328013371676207</v>
+        <v>0.1238548830151558</v>
       </c>
       <c r="CX5" t="n">
-        <v>0.0004025225643999875</v>
+        <v>0.008933043107390404</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.0005205312045291066</v>
+        <v>0.07208822667598724</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.0003558421449270099</v>
+        <v>0.01163786184042692</v>
       </c>
       <c r="DA5" t="n">
-        <v>5.724757102143485e-06</v>
+        <v>0.002859430387616158</v>
       </c>
       <c r="DB5" t="n">
-        <v>0.0003292656328994781</v>
+        <v>0.01149069983512163</v>
       </c>
       <c r="DC5" t="n">
-        <v>0.0002018747327383608</v>
+        <v>0.005650115199387074</v>
       </c>
       <c r="DD5" t="n">
-        <v>6.101388862589374e-05</v>
+        <v>0.02011065930128098</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.0005139971617609262</v>
+        <v>0.05783835425972939</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.001690530218183994</v>
+        <v>0.1292849481105804</v>
       </c>
       <c r="DG5" t="n">
-        <v>0.0001733720273477957</v>
+        <v>0.03704391419887543</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.0002512916107662022</v>
+        <v>0.08353300392627716</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.0007479207706637681</v>
+        <v>0.02717253938317299</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0.0001735321129672229</v>
+        <v>0.07978682219982147</v>
       </c>
       <c r="DK5" t="n">
-        <v>0.0001096877895179205</v>
+        <v>0.0008201291784644127</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.0001045075769070536</v>
+        <v>0.1035595536231995</v>
       </c>
       <c r="DM5" t="n">
-        <v>6.080311140976846e-05</v>
+        <v>0.005791901610791683</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.0003119795874226838</v>
+        <v>0.02256955951452255</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.0007164464914239943</v>
+        <v>0.03400024771690369</v>
       </c>
       <c r="DP5" t="n">
-        <v>0.0004579881788231432</v>
+        <v>0.02281335741281509</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0.0007979258662089705</v>
+        <v>0.01519998721778393</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.001003563404083252</v>
+        <v>0.03814850375056267</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.0002219535817857832</v>
+        <v>0.06100219488143921</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.0003074535052292049</v>
+        <v>0.005845934152603149</v>
       </c>
       <c r="DU5" t="n">
-        <v>0.0002669700479600579</v>
+        <v>0.07433398813009262</v>
       </c>
       <c r="DV5" t="n">
-        <v>0.0006867888732813299</v>
+        <v>0.08699677139520645</v>
       </c>
       <c r="DW5" t="n">
-        <v>2.414337359368801e-05</v>
+        <v>0.05763182044029236</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.0006290451274253428</v>
+        <v>0.04278021305799484</v>
       </c>
       <c r="DY5" t="n">
-        <v>0.0004271708312444389</v>
+        <v>0.006101894192397594</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0.0002009330783039331</v>
+        <v>0.03806324303150177</v>
       </c>
       <c r="EA5" t="n">
-        <v>9.319205128122121e-05</v>
+        <v>0.03585333377122879</v>
       </c>
       <c r="EB5" t="n">
-        <v>9.328759915661067e-05</v>
+        <v>0.04011369496583939</v>
       </c>
       <c r="EC5" t="n">
-        <v>0.0003098552697338164</v>
+        <v>0.01731615327298641</v>
       </c>
       <c r="ED5" t="n">
-        <v>0.0005619694129563868</v>
+        <v>0.1005571410059929</v>
       </c>
       <c r="EE5" t="n">
-        <v>0.0003133798018097878</v>
+        <v>0.05075842142105103</v>
       </c>
       <c r="EF5" t="n">
-        <v>0.000207303513889201</v>
+        <v>0.0189124308526516</v>
       </c>
       <c r="EG5" t="n">
-        <v>0.0008383993990719318</v>
+        <v>0.08488231152296066</v>
       </c>
       <c r="EH5" t="n">
-        <v>0.0005319229676388204</v>
+        <v>0.0208220724016428</v>
       </c>
       <c r="EI5" t="n">
-        <v>8.269932004623115e-05</v>
+        <v>0.04653147608041763</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.001166868605650961</v>
+        <v>0.007091356907039881</v>
       </c>
       <c r="EK5" t="n">
-        <v>0.0001003869547275826</v>
+        <v>0.002478263340890408</v>
       </c>
       <c r="EL5" t="n">
-        <v>0.0002303157816641033</v>
+        <v>0.01351215783506632</v>
       </c>
       <c r="EM5" t="n">
-        <v>0.0001753167452989146</v>
+        <v>0.009722205810248852</v>
       </c>
       <c r="EN5" t="n">
-        <v>0.0001090800215024501</v>
+        <v>0.007246371358633041</v>
       </c>
       <c r="EO5" t="n">
-        <v>0.0001712434750515968</v>
+        <v>0.0194195993244648</v>
       </c>
       <c r="EP5" t="n">
-        <v>0.001278315437957644</v>
+        <v>0.1098072975873947</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0.0005804304382763803</v>
+        <v>0.0265152994543314</v>
       </c>
       <c r="ER5" t="n">
-        <v>0.001254418049938977</v>
+        <v>0.05107816308736801</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.0006681704544462264</v>
+        <v>0.002450308762490749</v>
       </c>
       <c r="ET5" t="n">
-        <v>0.0001385167124681175</v>
+        <v>0.008309496566653252</v>
       </c>
       <c r="EU5" t="n">
-        <v>0.000492406077682972</v>
+        <v>0.03410045057535172</v>
       </c>
       <c r="EV5" t="n">
-        <v>0.0007572133326902986</v>
+        <v>0.02769102156162262</v>
       </c>
       <c r="EW5" t="n">
-        <v>0.0001389820827171206</v>
+        <v>0.03194084763526917</v>
       </c>
       <c r="EX5" t="n">
-        <v>1.364295167149976e-05</v>
+        <v>0.01201476529240608</v>
       </c>
       <c r="EY5" t="n">
-        <v>0.001452801749110222</v>
+        <v>0.1486527025699615</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0.0001490485301474109</v>
+        <v>0.002803338691592216</v>
       </c>
       <c r="FA5" t="n">
-        <v>0.0002672924310900271</v>
+        <v>0.07350586354732513</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.0003126610245089978</v>
+        <v>0.01611929759383202</v>
       </c>
       <c r="FC5" t="n">
-        <v>7.748136704321951e-05</v>
+        <v>0.01450622268021107</v>
       </c>
       <c r="FD5" t="n">
-        <v>0.0003031060041394085</v>
+        <v>0.02122316136956215</v>
       </c>
       <c r="FE5" t="n">
-        <v>0.0001841884368332103</v>
+        <v>0.0187445804476738</v>
       </c>
       <c r="FF5" t="n">
-        <v>8.795720350462943e-05</v>
+        <v>0.02068384923040867</v>
       </c>
       <c r="FG5" t="n">
-        <v>0.0002945602464023978</v>
+        <v>0.01696833409368992</v>
       </c>
       <c r="FH5" t="n">
-        <v>5.352207881514914e-05</v>
+        <v>0.06678739190101624</v>
       </c>
       <c r="FI5" t="n">
-        <v>0.001047254772856832</v>
+        <v>0.04785715416073799</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0.0003635581233538687</v>
+        <v>0.06323596835136414</v>
       </c>
       <c r="FK5" t="n">
-        <v>0.0003598174953367561</v>
+        <v>0.04586715996265411</v>
       </c>
       <c r="FL5" t="n">
-        <v>0.0005609766812995076</v>
+        <v>0.04310299456119537</v>
       </c>
       <c r="FM5" t="n">
-        <v>0.0001985447888728231</v>
+        <v>0.02272332459688187</v>
       </c>
       <c r="FN5" t="n">
-        <v>7.15961359674111e-05</v>
+        <v>0.01763710752129555</v>
       </c>
       <c r="FO5" t="n">
-        <v>0.0003486743080429733</v>
+        <v>0.06970247626304626</v>
       </c>
       <c r="FP5" t="n">
-        <v>0.0004796396242454648</v>
+        <v>0.05852215737104416</v>
       </c>
       <c r="FQ5" t="n">
-        <v>4.958517456543632e-05</v>
+        <v>0.09463974833488464</v>
       </c>
       <c r="FR5" t="n">
-        <v>0.001351238926872611</v>
+        <v>0.001116375438868999</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.0001115814520744607</v>
+        <v>0.07149535417556763</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.0001744720502756536</v>
+        <v>0.1962993741035461</v>
       </c>
       <c r="FU5" t="n">
-        <v>0.0005338880000635982</v>
+        <v>0.05263754352927208</v>
       </c>
       <c r="FV5" t="n">
-        <v>0.0008319912012666464</v>
+        <v>0.01520400028675795</v>
       </c>
       <c r="FW5" t="n">
-        <v>0.0004642739659175277</v>
+        <v>0.01622750423848629</v>
       </c>
       <c r="FX5" t="n">
-        <v>0.0004527760320343077</v>
+        <v>0.05648931115865707</v>
       </c>
       <c r="FY5" t="n">
-        <v>0.0007343774195760489</v>
+        <v>0.02396036311984062</v>
       </c>
       <c r="FZ5" t="n">
-        <v>6.462704186560586e-05</v>
+        <v>0.05955763161182404</v>
       </c>
       <c r="GA5" t="n">
-        <v>0.0002823741815518588</v>
+        <v>0.005130654200911522</v>
       </c>
       <c r="GB5" t="n">
-        <v>0.0003195651806890965</v>
+        <v>0.008118394762277603</v>
       </c>
       <c r="GC5" t="n">
-        <v>0.0006237422931008041</v>
+        <v>0.0321144312620163</v>
       </c>
       <c r="GD5" t="n">
-        <v>0.001102445530705154</v>
+        <v>0.0423743724822998</v>
       </c>
       <c r="GE5" t="n">
-        <v>0.002003165427595377</v>
+        <v>0.0647314041852951</v>
       </c>
       <c r="GF5" t="n">
-        <v>2.296591992489994e-05</v>
+        <v>0.03883639723062515</v>
       </c>
       <c r="GG5" t="n">
-        <v>0.0004988820292055607</v>
+        <v>0.02357167191803455</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.1189440041780472</v>
+        <v>1.092839056582307e-06</v>
       </c>
       <c r="B6" t="n">
-        <v>0.3273763358592987</v>
+        <v>3.952735369239235e-06</v>
       </c>
       <c r="C6" t="n">
-        <v>0.006473957560956478</v>
+        <v>1.100125132325047e-06</v>
       </c>
       <c r="D6" t="n">
-        <v>0.04147101938724518</v>
+        <v>9.612360827304656e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>0.06095825135707855</v>
+        <v>1.948910494320444e-06</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02423743717372417</v>
+        <v>8.862750746629899e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0581076480448246</v>
+        <v>8.72372538651689e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>0.03817301243543625</v>
+        <v>4.081703863789699e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01333295740187168</v>
+        <v>5.479977858158236e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1149717345833778</v>
+        <v>5.679009973391658e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2759225964546204</v>
+        <v>5.180509106139652e-06</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01381087675690651</v>
+        <v>9.393412483404973e-07</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1152739524841309</v>
+        <v>1.577773559802154e-06</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1066891476511955</v>
+        <v>2.476589088473702e-06</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04347160831093788</v>
+        <v>1.509164775370664e-07</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0622248686850071</v>
+        <v>6.058339749870356e-07</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.05634737387299538</v>
+        <v>1.025925371322955e-06</v>
       </c>
       <c r="R6" t="n">
-        <v>0.01614700257778168</v>
+        <v>6.561653549397306e-07</v>
       </c>
       <c r="S6" t="n">
-        <v>0.008113695308566093</v>
+        <v>2.547351130033348e-07</v>
       </c>
       <c r="T6" t="n">
-        <v>0.08702922612428665</v>
+        <v>6.614793619519332e-07</v>
       </c>
       <c r="U6" t="n">
-        <v>0.007586373016238213</v>
+        <v>2.621030716909445e-07</v>
       </c>
       <c r="V6" t="n">
-        <v>0.02610142715275288</v>
+        <v>2.430803647257562e-07</v>
       </c>
       <c r="W6" t="n">
-        <v>0.05143314599990845</v>
+        <v>2.103205076764425e-07</v>
       </c>
       <c r="X6" t="n">
-        <v>0.04380623251199722</v>
+        <v>7.470524820973878e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.02279200404882431</v>
+        <v>9.236823217406709e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0155473044142127</v>
+        <v>3.510966735120746e-07</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.01090394705533981</v>
+        <v>4.170857721419452e-07</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.0769178718328476</v>
+        <v>1.245697376361932e-07</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.1089427396655083</v>
+        <v>3.120536717915456e-08</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.02963165566325188</v>
+        <v>8.654350835968216e-07</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.02858086302876472</v>
+        <v>5.290231683829916e-07</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.003091637045145035</v>
+        <v>1.135208975711066e-07</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.008254643529653549</v>
+        <v>3.494599241093965e-07</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.07710748910903931</v>
+        <v>2.227294970680305e-07</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.004146202467381954</v>
+        <v>9.336133075521502e-07</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.01889517530798912</v>
+        <v>3.69764450169896e-07</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.007929922081530094</v>
+        <v>2.102094214251338e-07</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.06250373274087906</v>
+        <v>1.460149405829725e-06</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.00750660290941596</v>
+        <v>9.979892467981699e-09</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.02995060384273529</v>
+        <v>2.510451224679855e-07</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.01011082902550697</v>
+        <v>8.370429327442253e-07</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.03783203288912773</v>
+        <v>4.446648347311566e-07</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.02072663977742195</v>
+        <v>1.901011046356871e-07</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.006047537550330162</v>
+        <v>4.745029968944436e-07</v>
       </c>
       <c r="AS6" t="n">
-        <v>0.02882274053990841</v>
+        <v>1.156263920165657e-07</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.006971693132072687</v>
+        <v>1.64762496979165e-07</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.1793629676103592</v>
+        <v>3.661861455839244e-06</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.03915448486804962</v>
+        <v>5.228914687904762e-07</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.004462199285626411</v>
+        <v>3.015969127773133e-07</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.03801661729812622</v>
+        <v>7.774792152304144e-07</v>
       </c>
       <c r="AY6" t="n">
-        <v>0.03486742079257965</v>
+        <v>2.327155073089671e-07</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.03704570978879929</v>
+        <v>2.678652890608646e-07</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.01032088417559862</v>
+        <v>2.591391705664137e-07</v>
       </c>
       <c r="BB6" t="n">
-        <v>0.02336134761571884</v>
+        <v>2.011896640397026e-07</v>
       </c>
       <c r="BC6" t="n">
-        <v>0.006503567099571228</v>
+        <v>9.934703939507017e-07</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.03963200375437737</v>
+        <v>4.74118763804654e-07</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.03860895335674286</v>
+        <v>1.227068878506543e-06</v>
       </c>
       <c r="BF6" t="n">
-        <v>0.02142493799328804</v>
+        <v>6.488683368388592e-08</v>
       </c>
       <c r="BG6" t="n">
-        <v>0.111583910882473</v>
+        <v>8.442407306574751e-07</v>
       </c>
       <c r="BH6" t="n">
-        <v>0.01012685894966125</v>
+        <v>3.431189838920545e-07</v>
       </c>
       <c r="BI6" t="n">
-        <v>0.07049764692783356</v>
+        <v>1.386435997119406e-07</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.03800270706415176</v>
+        <v>1.837375975810573e-07</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.006077651400119066</v>
+        <v>3.545490301348764e-07</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.01721764542162418</v>
+        <v>1.871607508974193e-07</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.04208151996135712</v>
+        <v>1.189995089134754e-07</v>
       </c>
       <c r="BN6" t="n">
-        <v>0.005926678888499737</v>
+        <v>2.022523943878696e-07</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.01424987241625786</v>
+        <v>4.212487425547806e-08</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.01495947036892176</v>
+        <v>7.606853955621773e-07</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.06015831977128983</v>
+        <v>2.709838611281157e-07</v>
       </c>
       <c r="BR6" t="n">
-        <v>0.001273253932595253</v>
+        <v>6.717647806908644e-07</v>
       </c>
       <c r="BS6" t="n">
-        <v>0.03776116669178009</v>
+        <v>1.70509153463172e-07</v>
       </c>
       <c r="BT6" t="n">
-        <v>0.04146083444356918</v>
+        <v>4.205873551654804e-07</v>
       </c>
       <c r="BU6" t="n">
-        <v>3.492832183837891e-05</v>
+        <v>3.320384394100984e-07</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.1367627829313278</v>
+        <v>3.18996762871393e-06</v>
       </c>
       <c r="BW6" t="n">
-        <v>0.04591915011405945</v>
+        <v>1.761845709324916e-07</v>
       </c>
       <c r="BX6" t="n">
-        <v>0.008540503680706024</v>
+        <v>5.246536147751613e-07</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.01895837858319283</v>
+        <v>2.750211365309951e-07</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0.007317683193832636</v>
+        <v>2.235118898852306e-07</v>
       </c>
       <c r="CA6" t="n">
-        <v>0.006314943078905344</v>
+        <v>2.803757581659738e-07</v>
       </c>
       <c r="CB6" t="n">
-        <v>0.03615861758589745</v>
+        <v>1.587062286034779e-07</v>
       </c>
       <c r="CC6" t="n">
-        <v>0.003530249232426286</v>
+        <v>4.558368118523504e-07</v>
       </c>
       <c r="CD6" t="n">
-        <v>0.01533657591789961</v>
+        <v>1.269997369490738e-07</v>
       </c>
       <c r="CE6" t="n">
-        <v>0.06396562606096268</v>
+        <v>1.365452362733777e-06</v>
       </c>
       <c r="CF6" t="n">
-        <v>0.001965295290574431</v>
+        <v>3.645959054665582e-07</v>
       </c>
       <c r="CG6" t="n">
-        <v>0.0001340918242931366</v>
+        <v>1.352565881518331e-08</v>
       </c>
       <c r="CH6" t="n">
-        <v>0.00692044198513031</v>
+        <v>3.765566134461551e-07</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.001648673322051764</v>
+        <v>2.974092012664187e-07</v>
       </c>
       <c r="CJ6" t="n">
-        <v>0.01169740315526724</v>
+        <v>2.436135915218074e-08</v>
       </c>
       <c r="CK6" t="n">
-        <v>0.002067681401968002</v>
+        <v>2.553149158757151e-07</v>
       </c>
       <c r="CL6" t="n">
-        <v>0.008598750457167625</v>
+        <v>2.390227393789246e-07</v>
       </c>
       <c r="CM6" t="n">
-        <v>0.08157867193222046</v>
+        <v>3.924538702904101e-07</v>
       </c>
       <c r="CN6" t="n">
-        <v>0.02669727057218552</v>
+        <v>2.438195224385709e-06</v>
       </c>
       <c r="CO6" t="n">
-        <v>0.01450373511761427</v>
+        <v>5.465980166263762e-07</v>
       </c>
       <c r="CP6" t="n">
-        <v>0.0456879585981369</v>
+        <v>2.655524866668202e-08</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.04731708765029907</v>
+        <v>1.301894911875934e-07</v>
       </c>
       <c r="CR6" t="n">
-        <v>0.0003174520097672939</v>
+        <v>9.958398550224956e-08</v>
       </c>
       <c r="CS6" t="n">
-        <v>0.01412600930780172</v>
+        <v>3.047971688374673e-07</v>
       </c>
       <c r="CT6" t="n">
-        <v>0.005372907500714064</v>
+        <v>6.910771048751485e-07</v>
       </c>
       <c r="CU6" t="n">
-        <v>0.05736361816525459</v>
+        <v>1.2900034107588e-07</v>
       </c>
       <c r="CV6" t="n">
-        <v>0.00869942270219326</v>
+        <v>7.183682271261205e-08</v>
       </c>
       <c r="CW6" t="n">
-        <v>0.06891472637653351</v>
+        <v>1.371886469314632e-06</v>
       </c>
       <c r="CX6" t="n">
-        <v>0.0110264616087079</v>
+        <v>3.575812286271685e-07</v>
       </c>
       <c r="CY6" t="n">
-        <v>0.004892421886324883</v>
+        <v>2.742307287917356e-07</v>
       </c>
       <c r="CZ6" t="n">
-        <v>0.01832225359976292</v>
+        <v>1.73732615849076e-07</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.009009843692183495</v>
+        <v>2.452276817166421e-07</v>
       </c>
       <c r="DB6" t="n">
-        <v>0.01322883553802967</v>
+        <v>1.370148510204672e-07</v>
       </c>
       <c r="DC6" t="n">
-        <v>0.009217346087098122</v>
+        <v>3.099846992427047e-07</v>
       </c>
       <c r="DD6" t="n">
-        <v>0.01007519010454416</v>
+        <v>3.707544635744853e-07</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.01252041663974524</v>
+        <v>4.173758156866825e-07</v>
       </c>
       <c r="DF6" t="n">
-        <v>0.03458185866475105</v>
+        <v>1.53452560880396e-06</v>
       </c>
       <c r="DG6" t="n">
-        <v>0.03044756315648556</v>
+        <v>1.073981650279165e-07</v>
       </c>
       <c r="DH6" t="n">
-        <v>0.06031609699130058</v>
+        <v>1.077833360341174e-07</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.004380024969577789</v>
+        <v>1.093997425982707e-08</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0.01408976968377829</v>
+        <v>8.280687211481563e-07</v>
       </c>
       <c r="DK6" t="n">
-        <v>0.01392105966806412</v>
+        <v>1.052515798960485e-07</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.05015251040458679</v>
+        <v>1.947927046330733e-07</v>
       </c>
       <c r="DM6" t="n">
-        <v>0.04891153052449226</v>
+        <v>2.223588353444939e-07</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.01588314026594162</v>
+        <v>1.965791369684666e-07</v>
       </c>
       <c r="DO6" t="n">
-        <v>0.02901920676231384</v>
+        <v>7.086918003551546e-07</v>
       </c>
       <c r="DP6" t="n">
-        <v>0.01019477099180222</v>
+        <v>7.083329478518863e-08</v>
       </c>
       <c r="DQ6" t="n">
-        <v>0.02798137441277504</v>
+        <v>2.874539006825216e-08</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.006818837951868773</v>
+        <v>2.948779709299743e-08</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.03102836944162846</v>
+        <v>2.56281396104896e-08</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.006781822070479393</v>
+        <v>1.687377277903579e-07</v>
       </c>
       <c r="DU6" t="n">
-        <v>0.008381757885217667</v>
+        <v>6.559048415510915e-07</v>
       </c>
       <c r="DV6" t="n">
-        <v>0.002532090991735458</v>
+        <v>5.921288561694382e-07</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.007964524440467358</v>
+        <v>6.912927119628876e-07</v>
       </c>
       <c r="DX6" t="n">
-        <v>0.0414360910654068</v>
+        <v>1.048723333951784e-06</v>
       </c>
       <c r="DY6" t="n">
-        <v>0.01239020004868507</v>
+        <v>9.42932771863525e-08</v>
       </c>
       <c r="DZ6" t="n">
-        <v>0.002489432226866484</v>
+        <v>2.036252624293411e-07</v>
       </c>
       <c r="EA6" t="n">
-        <v>0.001374563784338534</v>
+        <v>5.957984967608354e-07</v>
       </c>
       <c r="EB6" t="n">
-        <v>0.04315458610653877</v>
+        <v>1.037334413922508e-06</v>
       </c>
       <c r="EC6" t="n">
-        <v>0.001939695095643401</v>
+        <v>7.189578354882542e-08</v>
       </c>
       <c r="ED6" t="n">
-        <v>0.05360148847103119</v>
+        <v>3.581266412311379e-07</v>
       </c>
       <c r="EE6" t="n">
-        <v>0.01640479639172554</v>
+        <v>7.487002449124702e-07</v>
       </c>
       <c r="EF6" t="n">
-        <v>0.01897070743143559</v>
+        <v>3.251058160458342e-07</v>
       </c>
       <c r="EG6" t="n">
-        <v>0.04113705456256866</v>
+        <v>5.699232588085579e-07</v>
       </c>
       <c r="EH6" t="n">
-        <v>0.005183740518987179</v>
+        <v>7.890439945867911e-08</v>
       </c>
       <c r="EI6" t="n">
-        <v>0.06032324209809303</v>
+        <v>1.244336402805857e-07</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.005501370411366224</v>
+        <v>1.44232160437241e-07</v>
       </c>
       <c r="EK6" t="n">
-        <v>0.01028032600879669</v>
+        <v>4.784971565641172e-07</v>
       </c>
       <c r="EL6" t="n">
-        <v>0.02198813110589981</v>
+        <v>1.481149425330841e-08</v>
       </c>
       <c r="EM6" t="n">
-        <v>0.0008600973524153233</v>
+        <v>2.275786954442083e-07</v>
       </c>
       <c r="EN6" t="n">
-        <v>0.008950723335146904</v>
+        <v>1.805285592126893e-07</v>
       </c>
       <c r="EO6" t="n">
-        <v>0.02931934036314487</v>
+        <v>2.385408492955321e-07</v>
       </c>
       <c r="EP6" t="n">
-        <v>0.0556003637611866</v>
+        <v>8.213138471546699e-07</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0.03052734583616257</v>
+        <v>3.610340968407399e-07</v>
       </c>
       <c r="ER6" t="n">
-        <v>0.002801019931212068</v>
+        <v>9.461776784291942e-08</v>
       </c>
       <c r="ES6" t="n">
-        <v>0.003859718330204487</v>
+        <v>8.612989432776885e-08</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.0327971987426281</v>
+        <v>3.706186646468268e-08</v>
       </c>
       <c r="EU6" t="n">
-        <v>0.002957724034786224</v>
+        <v>7.738226770470646e-08</v>
       </c>
       <c r="EV6" t="n">
-        <v>0.03185970336198807</v>
+        <v>1.514690950443764e-07</v>
       </c>
       <c r="EW6" t="n">
-        <v>0.02647064998745918</v>
+        <v>1.107052156612554e-07</v>
       </c>
       <c r="EX6" t="n">
-        <v>0.002419352065771818</v>
+        <v>6.622424564284302e-08</v>
       </c>
       <c r="EY6" t="n">
-        <v>0.0697629526257515</v>
+        <v>1.57008696533012e-06</v>
       </c>
       <c r="EZ6" t="n">
-        <v>0.0004642581334337592</v>
+        <v>3.25450969285157e-07</v>
       </c>
       <c r="FA6" t="n">
-        <v>0.00309993838891387</v>
+        <v>5.283355619667418e-08</v>
       </c>
       <c r="FB6" t="n">
-        <v>0.02671186439692974</v>
+        <v>1.960343780638141e-07</v>
       </c>
       <c r="FC6" t="n">
-        <v>0.01040680706501007</v>
+        <v>2.588381562418363e-07</v>
       </c>
       <c r="FD6" t="n">
-        <v>0.002796656219288707</v>
+        <v>4.032440159562611e-09</v>
       </c>
       <c r="FE6" t="n">
-        <v>0.007978785783052444</v>
+        <v>3.01044053685473e-07</v>
       </c>
       <c r="FF6" t="n">
-        <v>0.0005979116540402174</v>
+        <v>3.70209988886927e-07</v>
       </c>
       <c r="FG6" t="n">
-        <v>0.005792185198515654</v>
+        <v>3.852745749099995e-07</v>
       </c>
       <c r="FH6" t="n">
-        <v>0.01748384535312653</v>
+        <v>6.422852720788796e-07</v>
       </c>
       <c r="FI6" t="n">
-        <v>0.02619433775544167</v>
+        <v>5.044586259828066e-07</v>
       </c>
       <c r="FJ6" t="n">
-        <v>0.04844056814908981</v>
+        <v>4.771677026838006e-07</v>
       </c>
       <c r="FK6" t="n">
-        <v>0.05474631488323212</v>
+        <v>2.917987558248569e-07</v>
       </c>
       <c r="FL6" t="n">
-        <v>0.01044008694589138</v>
+        <v>4.047356014780235e-07</v>
       </c>
       <c r="FM6" t="n">
-        <v>0.01391255762428045</v>
+        <v>1.602965369329468e-07</v>
       </c>
       <c r="FN6" t="n">
-        <v>0.009437522850930691</v>
+        <v>1.829787237284108e-07</v>
       </c>
       <c r="FO6" t="n">
-        <v>0.00265221856534481</v>
+        <v>6.240861694095656e-07</v>
       </c>
       <c r="FP6" t="n">
-        <v>0.04573382064700127</v>
+        <v>1.29743420984596e-06</v>
       </c>
       <c r="FQ6" t="n">
-        <v>0.08424657583236694</v>
+        <v>1.491828925281879e-06</v>
       </c>
       <c r="FR6" t="n">
-        <v>0.02067575044929981</v>
+        <v>8.632889603177318e-07</v>
       </c>
       <c r="FS6" t="n">
-        <v>0.004018025938421488</v>
+        <v>8.733867389310035e-07</v>
       </c>
       <c r="FT6" t="n">
-        <v>0.01405244693160057</v>
+        <v>1.161968498308852e-06</v>
       </c>
       <c r="FU6" t="n">
-        <v>0.01139726117253304</v>
+        <v>1.758957210995504e-07</v>
       </c>
       <c r="FV6" t="n">
-        <v>0.05334574729204178</v>
+        <v>3.847147809210583e-07</v>
       </c>
       <c r="FW6" t="n">
-        <v>0.03618868440389633</v>
+        <v>7.887595074862475e-07</v>
       </c>
       <c r="FX6" t="n">
-        <v>0.02290366776287556</v>
+        <v>1.064759885593958e-06</v>
       </c>
       <c r="FY6" t="n">
-        <v>0.06517157703638077</v>
+        <v>1.352808425281182e-07</v>
       </c>
       <c r="FZ6" t="n">
-        <v>0.01106620114296675</v>
+        <v>8.994175004772842e-07</v>
       </c>
       <c r="GA6" t="n">
-        <v>0.00643613189458847</v>
+        <v>3.097499359228095e-07</v>
       </c>
       <c r="GB6" t="n">
-        <v>0.01399582624435425</v>
+        <v>2.966401666526508e-07</v>
       </c>
       <c r="GC6" t="n">
-        <v>0.1006158888339996</v>
+        <v>4.443151624400343e-07</v>
       </c>
       <c r="GD6" t="n">
-        <v>0.04146204143762589</v>
+        <v>4.850996759842019e-08</v>
       </c>
       <c r="GE6" t="n">
-        <v>0.08630878478288651</v>
+        <v>3.663532481823495e-07</v>
       </c>
       <c r="GF6" t="n">
-        <v>0.03171105682849884</v>
+        <v>2.027438625873401e-07</v>
       </c>
       <c r="GG6" t="n">
-        <v>0.008207998238503933</v>
+        <v>3.908808139385656e-07</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.01553677208721638</v>
+        <v>0.2858137786388397</v>
       </c>
       <c r="B7" t="n">
-        <v>0.3246742784976959</v>
+        <v>1.241831183433533</v>
       </c>
       <c r="C7" t="n">
-        <v>0.03298629075288773</v>
+        <v>0.3055080473423004</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2208586484193802</v>
+        <v>1.140085935592651</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1181716769933701</v>
+        <v>0.3984149694442749</v>
       </c>
       <c r="F7" t="n">
-        <v>0.05183893814682961</v>
+        <v>0.3517434597015381</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01862822845578194</v>
+        <v>0.3611768186092377</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01174455136060715</v>
+        <v>0.2466536164283752</v>
       </c>
       <c r="I7" t="n">
-        <v>0.008197015151381493</v>
+        <v>0.09393284469842911</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01469456311315298</v>
+        <v>0.6298650503158569</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2680832743644714</v>
+        <v>1.160272359848022</v>
       </c>
       <c r="L7" t="n">
-        <v>0.003742560278624296</v>
+        <v>0.276040643453598</v>
       </c>
       <c r="M7" t="n">
-        <v>0.20633764564991</v>
+        <v>1.810776472091675</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1356692910194397</v>
+        <v>0.6311795711517334</v>
       </c>
       <c r="O7" t="n">
-        <v>0.03427775204181671</v>
+        <v>0.03784498572349548</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01558863185346127</v>
+        <v>0.3391939103603363</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.06653745472431183</v>
+        <v>0.06970043480396271</v>
       </c>
       <c r="R7" t="n">
-        <v>0.04028979688882828</v>
+        <v>0.1159493550658226</v>
       </c>
       <c r="S7" t="n">
-        <v>0.005891289561986923</v>
+        <v>0.02804946713149548</v>
       </c>
       <c r="T7" t="n">
-        <v>0.06633638590574265</v>
+        <v>0.3125225603580475</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0339445061981678</v>
+        <v>0.05414720624685287</v>
       </c>
       <c r="V7" t="n">
-        <v>0.01378082484006882</v>
+        <v>0.04968506097793579</v>
       </c>
       <c r="W7" t="n">
-        <v>0.05662358924746513</v>
+        <v>0.01344534009695053</v>
       </c>
       <c r="X7" t="n">
-        <v>0.06066049635410309</v>
+        <v>0.2237540930509567</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.04437525570392609</v>
+        <v>0.009490214288234711</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.01650749519467354</v>
+        <v>0.09898725152015686</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.02099256217479706</v>
+        <v>0.1714559197425842</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.03811749815940857</v>
+        <v>0.1460405588150024</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.03895321488380432</v>
+        <v>0.1919266879558563</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.007150211837142706</v>
+        <v>0.05772137641906738</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.002114383969455957</v>
+        <v>0.2465457916259766</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.01771051622927189</v>
+        <v>0.008776063099503517</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.01914722472429276</v>
+        <v>0.03583478927612305</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.03601496294140816</v>
+        <v>0.1353398263454437</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.005234431475400925</v>
+        <v>0.010361447930336</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.01485769730061293</v>
+        <v>0.124475322663784</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.02146148309111595</v>
+        <v>0.0874178558588028</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.03931284323334694</v>
+        <v>0.5823047161102295</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.005509860347956419</v>
+        <v>0.0009395400993525982</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.02381112240254879</v>
+        <v>0.05781936645507812</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.003320668358355761</v>
+        <v>0.5907768607139587</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.03095110133290291</v>
+        <v>0.3335534930229187</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.02381951734423637</v>
+        <v>0.1268894821405411</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.03461673110723495</v>
+        <v>0.1241188794374466</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.02306779846549034</v>
+        <v>0.03154951333999634</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.02881176769733429</v>
+        <v>0.1568967998027802</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.2277714312076569</v>
+        <v>1.055213570594788</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.01579220034182072</v>
+        <v>0.1626757383346558</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.04549454152584076</v>
+        <v>0.584291398525238</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.0157940499484539</v>
+        <v>0.427207738161087</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.00948777049779892</v>
+        <v>0.06952584534883499</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.001252328045666218</v>
+        <v>0.02398040890693665</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.06416169553995132</v>
+        <v>0.05139156430959702</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.01846905052661896</v>
+        <v>0.3207966983318329</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.02577758952975273</v>
+        <v>0.05122240632772446</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.03374209627509117</v>
+        <v>0.3881629407405853</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.05516134202480316</v>
+        <v>0.3831218481063843</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.04635014757514</v>
+        <v>0.007283303886651993</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.1127699092030525</v>
+        <v>0.2572782933712006</v>
       </c>
       <c r="BH7" t="n">
-        <v>0.01519889291375875</v>
+        <v>0.07425335794687271</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.07578258961439133</v>
+        <v>0.09703157097101212</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.07588331401348114</v>
+        <v>0.1375423967838287</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.02172918803989887</v>
+        <v>0.3821612000465393</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.07082401216030121</v>
+        <v>0.07453117519617081</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.01251776609569788</v>
+        <v>0.3252215683460236</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.000974675000179559</v>
+        <v>0.03081980720162392</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.002539209323003888</v>
+        <v>0.0360209047794342</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.03465893492102623</v>
+        <v>0.06050227582454681</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0.01921490579843521</v>
+        <v>0.1146605461835861</v>
       </c>
       <c r="BR7" t="n">
-        <v>0.03888216987252235</v>
+        <v>0.1057208478450775</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.05201374366879463</v>
+        <v>0.001910939812660217</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.02124561183154583</v>
+        <v>0.08284065127372742</v>
       </c>
       <c r="BU7" t="n">
-        <v>0.02275449968874454</v>
+        <v>0.1179831475019455</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.1304494440555573</v>
+        <v>0.7670266032218933</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.0191759280860424</v>
+        <v>0.03206365555524826</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.01153988391160965</v>
+        <v>0.5456051826477051</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.0227962750941515</v>
+        <v>0.1483556926250458</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0.01835884526371956</v>
+        <v>0.290133535861969</v>
       </c>
       <c r="CA7" t="n">
-        <v>0.004697786644101143</v>
+        <v>0.08046141266822815</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.01555224973708391</v>
+        <v>0.04736460000276566</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.01647810451686382</v>
+        <v>0.1110841184854507</v>
       </c>
       <c r="CD7" t="n">
-        <v>0.005977880209684372</v>
+        <v>0.08670643717050552</v>
       </c>
       <c r="CE7" t="n">
-        <v>0.04918923601508141</v>
+        <v>0.4037247002124786</v>
       </c>
       <c r="CF7" t="n">
-        <v>0.00674500735476613</v>
+        <v>0.07670604437589645</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.03357046470046043</v>
+        <v>0.3324311971664429</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.009346290491521358</v>
+        <v>0.0365057997405529</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.005223272368311882</v>
+        <v>0.04483125731348991</v>
       </c>
       <c r="CJ7" t="n">
-        <v>0.02254709973931313</v>
+        <v>0.01157482620328665</v>
       </c>
       <c r="CK7" t="n">
-        <v>0.0001632631756365299</v>
+        <v>0.07971042394638062</v>
       </c>
       <c r="CL7" t="n">
-        <v>0.007986264303326607</v>
+        <v>0.05974902957677841</v>
       </c>
       <c r="CM7" t="n">
-        <v>0.05146179348230362</v>
+        <v>0.1262706518173218</v>
       </c>
       <c r="CN7" t="n">
-        <v>0.01248551160097122</v>
+        <v>0.3735640645027161</v>
       </c>
       <c r="CO7" t="n">
-        <v>0.007895327173173428</v>
+        <v>0.1640100926160812</v>
       </c>
       <c r="CP7" t="n">
-        <v>0.07294417917728424</v>
+        <v>0.5157892107963562</v>
       </c>
       <c r="CQ7" t="n">
-        <v>0.07918274402618408</v>
+        <v>0.2832682728767395</v>
       </c>
       <c r="CR7" t="n">
-        <v>0.06956375390291214</v>
+        <v>0.08904172480106354</v>
       </c>
       <c r="CS7" t="n">
-        <v>0.01141375489532948</v>
+        <v>0.0728277862071991</v>
       </c>
       <c r="CT7" t="n">
-        <v>0.04955394938588142</v>
+        <v>0.0998874306678772</v>
       </c>
       <c r="CU7" t="n">
-        <v>0.01054047606885433</v>
+        <v>0.1371714770793915</v>
       </c>
       <c r="CV7" t="n">
-        <v>0.003061925992369652</v>
+        <v>0.1404812932014465</v>
       </c>
       <c r="CW7" t="n">
-        <v>0.05447560921311378</v>
+        <v>0.4370220899581909</v>
       </c>
       <c r="CX7" t="n">
-        <v>0.01460395660251379</v>
+        <v>0.04962943121790886</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.0444282591342926</v>
+        <v>0.3528970777988434</v>
       </c>
       <c r="CZ7" t="n">
-        <v>0.005135221406817436</v>
+        <v>0.03360579162836075</v>
       </c>
       <c r="DA7" t="n">
-        <v>0.01546394638717175</v>
+        <v>0.02612209692597389</v>
       </c>
       <c r="DB7" t="n">
-        <v>0.02543693594634533</v>
+        <v>0.03935214132070541</v>
       </c>
       <c r="DC7" t="n">
-        <v>0.004744221456348896</v>
+        <v>0.04837927222251892</v>
       </c>
       <c r="DD7" t="n">
-        <v>0.0004020398482680321</v>
+        <v>0.08061899244785309</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.005939197726547718</v>
+        <v>0.2735196650028229</v>
       </c>
       <c r="DF7" t="n">
-        <v>0.0682576522231102</v>
+        <v>0.5068858861923218</v>
       </c>
       <c r="DG7" t="n">
-        <v>0.02437205612659454</v>
+        <v>0.2213019132614136</v>
       </c>
       <c r="DH7" t="n">
-        <v>0.09255193918943405</v>
+        <v>0.5231010317802429</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.1318951547145844</v>
+        <v>0.08041682839393616</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0.007799382787197828</v>
+        <v>0.6000789999961853</v>
       </c>
       <c r="DK7" t="n">
-        <v>0.01113903429359198</v>
+        <v>0.06743183732032776</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.02533969655632973</v>
+        <v>0.4882329702377319</v>
       </c>
       <c r="DM7" t="n">
-        <v>0.02441796660423279</v>
+        <v>0.05127881839871407</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.01022432185709476</v>
+        <v>0.1168286427855492</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.04413928091526031</v>
+        <v>0.2020483911037445</v>
       </c>
       <c r="DP7" t="n">
-        <v>0.0408998541533947</v>
+        <v>0.009778786450624466</v>
       </c>
       <c r="DQ7" t="n">
-        <v>0.02179502323269844</v>
+        <v>0.237890750169754</v>
       </c>
       <c r="DR7" t="n">
-        <v>0.06255939602851868</v>
+        <v>0.2150740027427673</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.003199012018740177</v>
+        <v>0.05120811611413956</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.002317187841981649</v>
+        <v>0.06760621070861816</v>
       </c>
       <c r="DU7" t="n">
-        <v>0.01445528864860535</v>
+        <v>0.1341018825769424</v>
       </c>
       <c r="DV7" t="n">
-        <v>0.01141994632780552</v>
+        <v>0.421383798122406</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.01806297898292542</v>
+        <v>0.06901164352893829</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.00798125471919775</v>
+        <v>0.1750210225582123</v>
       </c>
       <c r="DY7" t="n">
-        <v>0.0467703752219677</v>
+        <v>0.04124060645699501</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0.01039709523320198</v>
+        <v>0.3246393203735352</v>
       </c>
       <c r="EA7" t="n">
-        <v>0.03675123676657677</v>
+        <v>0.04887138679623604</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.02863191068172455</v>
+        <v>0.3461036086082458</v>
       </c>
       <c r="EC7" t="n">
-        <v>0.005882307887077332</v>
+        <v>0.01804091222584248</v>
       </c>
       <c r="ED7" t="n">
-        <v>0.03054618835449219</v>
+        <v>0.4467115700244904</v>
       </c>
       <c r="EE7" t="n">
-        <v>0.003973583225160837</v>
+        <v>0.3538605868816376</v>
       </c>
       <c r="EF7" t="n">
-        <v>0.00478716753423214</v>
+        <v>0.2354325652122498</v>
       </c>
       <c r="EG7" t="n">
-        <v>0.04427479207515717</v>
+        <v>0.3223814368247986</v>
       </c>
       <c r="EH7" t="n">
-        <v>0.006658046040683985</v>
+        <v>0.02985828369855881</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.02837828360497952</v>
+        <v>0.2078714668750763</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.09126313030719757</v>
+        <v>0.06287246942520142</v>
       </c>
       <c r="EK7" t="n">
-        <v>0.004756069742143154</v>
+        <v>0.1100272387266159</v>
       </c>
       <c r="EL7" t="n">
-        <v>0.04653575271368027</v>
+        <v>0.006096940487623215</v>
       </c>
       <c r="EM7" t="n">
-        <v>0.007478091865777969</v>
+        <v>0.0509689562022686</v>
       </c>
       <c r="EN7" t="n">
-        <v>0.01111418195068836</v>
+        <v>0.05246420204639435</v>
       </c>
       <c r="EO7" t="n">
-        <v>0.003695574356243014</v>
+        <v>0.1517752707004547</v>
       </c>
       <c r="EP7" t="n">
-        <v>0.02857118472456932</v>
+        <v>0.3789326846599579</v>
       </c>
       <c r="EQ7" t="n">
-        <v>0.03931061923503876</v>
+        <v>0.1136809661984444</v>
       </c>
       <c r="ER7" t="n">
-        <v>0.03666131198406219</v>
+        <v>0.264152318239212</v>
       </c>
       <c r="ES7" t="n">
-        <v>0.03336169943213463</v>
+        <v>0.1122913062572479</v>
       </c>
       <c r="ET7" t="n">
-        <v>0.04648436233401299</v>
+        <v>0.3483076095581055</v>
       </c>
       <c r="EU7" t="n">
-        <v>0.02759884297847748</v>
+        <v>0.1213369444012642</v>
       </c>
       <c r="EV7" t="n">
-        <v>0.007819603197276592</v>
+        <v>0.05686772614717484</v>
       </c>
       <c r="EW7" t="n">
-        <v>0.007188713178038597</v>
+        <v>0.1446837335824966</v>
       </c>
       <c r="EX7" t="n">
-        <v>0.002870652358978987</v>
+        <v>0.0992315337061882</v>
       </c>
       <c r="EY7" t="n">
-        <v>0.05661601200699806</v>
+        <v>0.4770054817199707</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0.005832502618432045</v>
+        <v>0.05029178038239479</v>
       </c>
       <c r="FA7" t="n">
-        <v>0.04266376793384552</v>
+        <v>0.403850644826889</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.005297894589602947</v>
+        <v>0.03184229880571365</v>
       </c>
       <c r="FC7" t="n">
-        <v>0.01353409979492426</v>
+        <v>0.01926536858081818</v>
       </c>
       <c r="FD7" t="n">
-        <v>0.02829105779528618</v>
+        <v>0.03806546702980995</v>
       </c>
       <c r="FE7" t="n">
-        <v>0.005187994800508022</v>
+        <v>0.1051829382777214</v>
       </c>
       <c r="FF7" t="n">
-        <v>0.006574118509888649</v>
+        <v>0.06097391992807388</v>
       </c>
       <c r="FG7" t="n">
-        <v>0.006712157744914293</v>
+        <v>0.02747678384184837</v>
       </c>
       <c r="FH7" t="n">
-        <v>0.01950161717832088</v>
+        <v>0.1613621711730957</v>
       </c>
       <c r="FI7" t="n">
-        <v>0.008315927349030972</v>
+        <v>0.2493830323219299</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0.02389886043965816</v>
+        <v>0.08713382482528687</v>
       </c>
       <c r="FK7" t="n">
-        <v>0.01536370813846588</v>
+        <v>0.03335050493478775</v>
       </c>
       <c r="FL7" t="n">
-        <v>0.01589903049170971</v>
+        <v>0.1119327396154404</v>
       </c>
       <c r="FM7" t="n">
-        <v>0.001726501621305943</v>
+        <v>0.005058098584413528</v>
       </c>
       <c r="FN7" t="n">
-        <v>0.009671379812061787</v>
+        <v>0.03347690403461456</v>
       </c>
       <c r="FO7" t="n">
-        <v>0.02545376308262348</v>
+        <v>0.3186104595661163</v>
       </c>
       <c r="FP7" t="n">
-        <v>0.0005235979333519936</v>
+        <v>0.03441059961915016</v>
       </c>
       <c r="FQ7" t="n">
-        <v>0.002909008646383882</v>
+        <v>0.492677628993988</v>
       </c>
       <c r="FR7" t="n">
-        <v>0.009075908921658993</v>
+        <v>0.3292664587497711</v>
       </c>
       <c r="FS7" t="n">
-        <v>0.02276140451431274</v>
+        <v>0.6805994510650635</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.03175828605890274</v>
+        <v>0.2678990364074707</v>
       </c>
       <c r="FU7" t="n">
-        <v>0.002016801387071609</v>
+        <v>0.03243952244520187</v>
       </c>
       <c r="FV7" t="n">
-        <v>0.05716662853956223</v>
+        <v>0.02090534567832947</v>
       </c>
       <c r="FW7" t="n">
-        <v>0.02251607179641724</v>
+        <v>0.006624776870012283</v>
       </c>
       <c r="FX7" t="n">
-        <v>0.02150349505245686</v>
+        <v>0.3517498672008514</v>
       </c>
       <c r="FY7" t="n">
-        <v>0.02952164225280285</v>
+        <v>0.07128511369228363</v>
       </c>
       <c r="FZ7" t="n">
-        <v>0.01520632673054934</v>
+        <v>0.3004933893680573</v>
       </c>
       <c r="GA7" t="n">
-        <v>0.02027116902172565</v>
+        <v>0.1491533070802689</v>
       </c>
       <c r="GB7" t="n">
-        <v>0.02066707611083984</v>
+        <v>0.204194039106369</v>
       </c>
       <c r="GC7" t="n">
-        <v>0.02084376476705074</v>
+        <v>0.3635571897029877</v>
       </c>
       <c r="GD7" t="n">
-        <v>0.02533010020852089</v>
+        <v>0.03865513205528259</v>
       </c>
       <c r="GE7" t="n">
-        <v>0.09630932658910751</v>
+        <v>0.2971271872520447</v>
       </c>
       <c r="GF7" t="n">
-        <v>0.02507166564464569</v>
+        <v>0.08156374096870422</v>
       </c>
       <c r="GG7" t="n">
-        <v>0.01245689392089844</v>
+        <v>0.05212181806564331</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.002229845151305199</v>
+        <v>0.1936893463134766</v>
       </c>
       <c r="B8" t="n">
-        <v>0.03087601438164711</v>
+        <v>0.6679883003234863</v>
       </c>
       <c r="C8" t="n">
-        <v>0.002673916751518846</v>
+        <v>0.01815389841794968</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0148210683837533</v>
+        <v>0.179580420255661</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002538510598242283</v>
+        <v>0.05956567078828812</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01915733329951763</v>
+        <v>0.6458630561828613</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0004482034128159285</v>
+        <v>0.1252977252006531</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01003915257751942</v>
+        <v>0.2534731328487396</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001948342425748706</v>
+        <v>0.005353102460503578</v>
       </c>
       <c r="J8" t="n">
-        <v>0.006585059221833944</v>
+        <v>0.2218905985355377</v>
       </c>
       <c r="K8" t="n">
-        <v>0.02441627904772758</v>
+        <v>0.8952403664588928</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0009693439933471382</v>
+        <v>0.07146742939949036</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0140420887619257</v>
+        <v>0.1864087730646133</v>
       </c>
       <c r="N8" t="n">
-        <v>0.002368811285123229</v>
+        <v>0.2384918034076691</v>
       </c>
       <c r="O8" t="n">
-        <v>0.02140353247523308</v>
+        <v>0.5816437005996704</v>
       </c>
       <c r="P8" t="n">
-        <v>0.001743101049214602</v>
+        <v>0.007209604140371084</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.0009494652040302753</v>
+        <v>0.02937684394419193</v>
       </c>
       <c r="R8" t="n">
-        <v>0.00198216550052166</v>
+        <v>0.03624613955616951</v>
       </c>
       <c r="S8" t="n">
-        <v>0.00241448450833559</v>
+        <v>0.007895084097981453</v>
       </c>
       <c r="T8" t="n">
-        <v>0.004592868033796549</v>
+        <v>0.01694812253117561</v>
       </c>
       <c r="U8" t="n">
-        <v>0.001943579874932766</v>
+        <v>0.1408699303865433</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0002203476033173501</v>
+        <v>0.09751802682876587</v>
       </c>
       <c r="W8" t="n">
-        <v>0.001313783344812691</v>
+        <v>0.1082706823945045</v>
       </c>
       <c r="X8" t="n">
-        <v>0.0007767742499709129</v>
+        <v>0.08481685817241669</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.003242193255573511</v>
+        <v>0.07128779590129852</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.002710959641262889</v>
+        <v>0.1464607268571854</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.001637774985283613</v>
+        <v>0.01133435219526291</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.001677593449130654</v>
+        <v>0.03503376618027687</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.004781659226864576</v>
+        <v>0.05694952979683876</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.0001875403977464885</v>
+        <v>0.08313342928886414</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.0004251234931871295</v>
+        <v>0.08801800012588501</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.001965068513527513</v>
+        <v>0.186953216791153</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.003388423006981611</v>
+        <v>0.03810548037290573</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.001752510783262551</v>
+        <v>0.03494306281208992</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.00188314716797322</v>
+        <v>0.2730673253536224</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.001205424079671502</v>
+        <v>0.02288400754332542</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.002434864174574614</v>
+        <v>0.003383532166481018</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.005218497011810541</v>
+        <v>0.003339957445859909</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.0003798832185566425</v>
+        <v>0.1115303933620453</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.001519645098596811</v>
+        <v>0.09550213068723679</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.004119849298149347</v>
+        <v>0.08593370020389557</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.004661980085074902</v>
+        <v>0.07688643038272858</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.00175646529532969</v>
+        <v>0.1343896985054016</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.001914343563839793</v>
+        <v>0.2020837515592575</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.004038885701447725</v>
+        <v>0.06232409551739693</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.001704959431663156</v>
+        <v>0.1508219838142395</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.01969866827130318</v>
+        <v>0.6483704447746277</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.00033425388392061</v>
+        <v>0.08644950389862061</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.0004305198090150952</v>
+        <v>0.1000347137451172</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.002245359122753143</v>
+        <v>0.1796387732028961</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.01443356927484274</v>
+        <v>0.2266217768192291</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.003826883621513844</v>
+        <v>0.003392274025827646</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.005961858667433262</v>
+        <v>0.002579783089458942</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.005125768948346376</v>
+        <v>0.001293594017624855</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.0008480867836624384</v>
+        <v>0.02336318790912628</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.005901495460420847</v>
+        <v>0.1109949722886086</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.008111624047160149</v>
+        <v>0.08507231622934341</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.004006081726402044</v>
+        <v>0.09624770283699036</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.008186819031834602</v>
+        <v>0.01612618565559387</v>
       </c>
       <c r="BH8" t="n">
-        <v>0.005844155326485634</v>
+        <v>0.2520854473114014</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.002459231065586209</v>
+        <v>0.07361824810504913</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.006455097813159227</v>
+        <v>0.1424299329519272</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.002480663824826479</v>
+        <v>0.03354692086577415</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.0001818640303099528</v>
+        <v>0.02977442741394043</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.001946880947798491</v>
+        <v>0.2206816226243973</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.00390668585896492</v>
+        <v>0.02104688994586468</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.003107783850282431</v>
+        <v>0.0273645706474781</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.0003173144650645554</v>
+        <v>0.1032632440328598</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0.001035268534906209</v>
+        <v>0.1072913929820061</v>
       </c>
       <c r="BR8" t="n">
-        <v>0.00290660560131073</v>
+        <v>0.2707251012325287</v>
       </c>
       <c r="BS8" t="n">
-        <v>0.002054509241133928</v>
+        <v>0.006686197593808174</v>
       </c>
       <c r="BT8" t="n">
-        <v>4.153861664235592e-05</v>
+        <v>0.04447660595178604</v>
       </c>
       <c r="BU8" t="n">
-        <v>0.001250541536137462</v>
+        <v>0.05254925787448883</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.009940257295966148</v>
+        <v>0.3930101096630096</v>
       </c>
       <c r="BW8" t="n">
-        <v>0.004270616918802261</v>
+        <v>0.08347977697849274</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.0004331453237682581</v>
+        <v>0.1027946993708611</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.002071622526273131</v>
+        <v>0.02383055537939072</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.006616040132939816</v>
+        <v>0.1265549212694168</v>
       </c>
       <c r="CA8" t="n">
-        <v>0.001327976817265153</v>
+        <v>0.1169168055057526</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.003513654693961143</v>
+        <v>0.07981276512145996</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.003572984132915735</v>
+        <v>0.040427565574646</v>
       </c>
       <c r="CD8" t="n">
-        <v>0.0002355419564992189</v>
+        <v>0.05511917546391487</v>
       </c>
       <c r="CE8" t="n">
-        <v>0.005539456382393837</v>
+        <v>0.1920249462127686</v>
       </c>
       <c r="CF8" t="n">
-        <v>0.003374658524990082</v>
+        <v>0.0004334701225161552</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.002712148008868098</v>
+        <v>0.02885564416646957</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.001916660461574793</v>
+        <v>0.02030020579695702</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.002502024406567216</v>
+        <v>0.1848867237567902</v>
       </c>
       <c r="CJ8" t="n">
-        <v>0.002490667160600424</v>
+        <v>0.06762770563364029</v>
       </c>
       <c r="CK8" t="n">
-        <v>0.001454648561775684</v>
+        <v>0.02670334279537201</v>
       </c>
       <c r="CL8" t="n">
-        <v>0.001641926704905927</v>
+        <v>0.01467858999967575</v>
       </c>
       <c r="CM8" t="n">
-        <v>0.004126413259655237</v>
+        <v>0.1105222031474113</v>
       </c>
       <c r="CN8" t="n">
-        <v>0.001119192223995924</v>
+        <v>0.3749593794345856</v>
       </c>
       <c r="CO8" t="n">
-        <v>0.00075813930016011</v>
+        <v>0.2002377808094025</v>
       </c>
       <c r="CP8" t="n">
-        <v>0.008148989640176296</v>
+        <v>0.1199014708399773</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0.001735506346449256</v>
+        <v>0.03866998851299286</v>
       </c>
       <c r="CR8" t="n">
-        <v>0.0007656860398128629</v>
+        <v>0.07007328420877457</v>
       </c>
       <c r="CS8" t="n">
-        <v>0.0049416976980865</v>
+        <v>0.06412884593009949</v>
       </c>
       <c r="CT8" t="n">
-        <v>0.00558628560975194</v>
+        <v>0.00365616288036108</v>
       </c>
       <c r="CU8" t="n">
-        <v>0.0007352461107075214</v>
+        <v>0.0128512280061841</v>
       </c>
       <c r="CV8" t="n">
-        <v>9.045543265528977e-05</v>
+        <v>0.01474244147539139</v>
       </c>
       <c r="CW8" t="n">
-        <v>0.004914874676615</v>
+        <v>0.1763602644205093</v>
       </c>
       <c r="CX8" t="n">
-        <v>0.003436391474679112</v>
+        <v>0.03256923705339432</v>
       </c>
       <c r="CY8" t="n">
-        <v>0.00409940630197525</v>
+        <v>0.04601980373263359</v>
       </c>
       <c r="CZ8" t="n">
-        <v>0.00188560807146132</v>
+        <v>0.00365070067346096</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.002772362669929862</v>
+        <v>0.173530176281929</v>
       </c>
       <c r="DB8" t="n">
-        <v>0.002015781123191118</v>
+        <v>0.04648412764072418</v>
       </c>
       <c r="DC8" t="n">
-        <v>0.002778727328404784</v>
+        <v>0.01139307953417301</v>
       </c>
       <c r="DD8" t="n">
-        <v>0.001473316922783852</v>
+        <v>0.01456078141927719</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.003559024073183537</v>
+        <v>0.1459677219390869</v>
       </c>
       <c r="DF8" t="n">
-        <v>0.001935458625666797</v>
+        <v>0.1326271295547485</v>
       </c>
       <c r="DG8" t="n">
-        <v>0.0006319943349808455</v>
+        <v>0.1503732353448868</v>
       </c>
       <c r="DH8" t="n">
-        <v>0.005731379613280296</v>
+        <v>0.0170357134193182</v>
       </c>
       <c r="DI8" t="n">
-        <v>1.633816282264888e-05</v>
+        <v>0.2208300977945328</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0.00350335449911654</v>
+        <v>0.1161456704139709</v>
       </c>
       <c r="DK8" t="n">
-        <v>0.003729488933458924</v>
+        <v>0.08084052801132202</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.007653752807527781</v>
+        <v>0.1131196841597557</v>
       </c>
       <c r="DM8" t="n">
-        <v>0.003594352863729</v>
+        <v>0.05054214224219322</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.001838167430832982</v>
+        <v>0.1082530617713928</v>
       </c>
       <c r="DO8" t="n">
-        <v>0.0007463846122846007</v>
+        <v>0.1275862157344818</v>
       </c>
       <c r="DP8" t="n">
-        <v>0.00329028582200408</v>
+        <v>0.08552153408527374</v>
       </c>
       <c r="DQ8" t="n">
-        <v>0.002997264731675386</v>
+        <v>0.06464645266532898</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.001003387151286006</v>
+        <v>0.08190903067588806</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.000886131078004837</v>
+        <v>0.0734793022274971</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.001465413020923734</v>
+        <v>0.02756641060113907</v>
       </c>
       <c r="DU8" t="n">
-        <v>0.0005547984037548304</v>
+        <v>0.09766138345003128</v>
       </c>
       <c r="DV8" t="n">
-        <v>0.00286951893940568</v>
+        <v>0.00542009063065052</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.001120379660278559</v>
+        <v>0.08375950902700424</v>
       </c>
       <c r="DX8" t="n">
-        <v>0.002332506235688925</v>
+        <v>0.02118680998682976</v>
       </c>
       <c r="DY8" t="n">
-        <v>0.003724466543644667</v>
+        <v>0.005672264844179153</v>
       </c>
       <c r="DZ8" t="n">
-        <v>0.00392201030626893</v>
+        <v>0.1177972182631493</v>
       </c>
       <c r="EA8" t="n">
-        <v>0.0007092097075656056</v>
+        <v>0.02961741201579571</v>
       </c>
       <c r="EB8" t="n">
-        <v>0.0004075614269822836</v>
+        <v>0.02374023757874966</v>
       </c>
       <c r="EC8" t="n">
-        <v>0.001257239142432809</v>
+        <v>0.01607179082930088</v>
       </c>
       <c r="ED8" t="n">
-        <v>0.0005759017658419907</v>
+        <v>0.005064865574240685</v>
       </c>
       <c r="EE8" t="n">
-        <v>0.001968691125512123</v>
+        <v>0.1368021965026855</v>
       </c>
       <c r="EF8" t="n">
-        <v>0.001520460238680243</v>
+        <v>0.05102698132395744</v>
       </c>
       <c r="EG8" t="n">
-        <v>0.004272979684174061</v>
+        <v>0.0171500388532877</v>
       </c>
       <c r="EH8" t="n">
-        <v>0.001866906997747719</v>
+        <v>0.09085411578416824</v>
       </c>
       <c r="EI8" t="n">
-        <v>0.001163851469755173</v>
+        <v>0.02352818660438061</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.0002106213651131839</v>
+        <v>0.04273474961519241</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.0003026289632543921</v>
+        <v>0.2653375566005707</v>
       </c>
       <c r="EL8" t="n">
-        <v>0.004274735227227211</v>
+        <v>0.02859096974134445</v>
       </c>
       <c r="EM8" t="n">
-        <v>0.0008010109304450452</v>
+        <v>0.02487329766154289</v>
       </c>
       <c r="EN8" t="n">
-        <v>0.0002430998429190367</v>
+        <v>0.01377193257212639</v>
       </c>
       <c r="EO8" t="n">
-        <v>0.0002863158006221056</v>
+        <v>0.05597157776355743</v>
       </c>
       <c r="EP8" t="n">
-        <v>0.002371483715251088</v>
+        <v>0.08419245481491089</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0.004327839706093073</v>
+        <v>0.1805337220430374</v>
       </c>
       <c r="ER8" t="n">
-        <v>0.002577440347522497</v>
+        <v>0.01172848138958216</v>
       </c>
       <c r="ES8" t="n">
-        <v>0.002038962207734585</v>
+        <v>0.1488860845565796</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.002348611829802394</v>
+        <v>0.05098912119865417</v>
       </c>
       <c r="EU8" t="n">
-        <v>0.003397181630134583</v>
+        <v>0.008796082809567451</v>
       </c>
       <c r="EV8" t="n">
-        <v>0.005238152109086514</v>
+        <v>0.0007444801740348339</v>
       </c>
       <c r="EW8" t="n">
-        <v>0.001338858157396317</v>
+        <v>0.04430224373936653</v>
       </c>
       <c r="EX8" t="n">
-        <v>0.0004177575756330043</v>
+        <v>0.04695853963494301</v>
       </c>
       <c r="EY8" t="n">
-        <v>0.004593012388795614</v>
+        <v>0.2000974118709564</v>
       </c>
       <c r="EZ8" t="n">
-        <v>0.002516754902899265</v>
+        <v>0.014469925314188</v>
       </c>
       <c r="FA8" t="n">
-        <v>0.002345819724723697</v>
+        <v>0.03320155292749405</v>
       </c>
       <c r="FB8" t="n">
-        <v>0.001966949552297592</v>
+        <v>0.02354398928582668</v>
       </c>
       <c r="FC8" t="n">
-        <v>0.002263432135805488</v>
+        <v>0.1625414043664932</v>
       </c>
       <c r="FD8" t="n">
-        <v>0.00310119055211544</v>
+        <v>0.07065694779157639</v>
       </c>
       <c r="FE8" t="n">
-        <v>0.001693319529294968</v>
+        <v>0.0315118245780468</v>
       </c>
       <c r="FF8" t="n">
-        <v>0.002584842965006828</v>
+        <v>0.009174130856990814</v>
       </c>
       <c r="FG8" t="n">
-        <v>0.0001583582197781652</v>
+        <v>0.03412079811096191</v>
       </c>
       <c r="FH8" t="n">
-        <v>0.001774804899469018</v>
+        <v>0.2031191140413284</v>
       </c>
       <c r="FI8" t="n">
-        <v>0.003927034325897694</v>
+        <v>0.1130677610635757</v>
       </c>
       <c r="FJ8" t="n">
-        <v>0.007229256443679333</v>
+        <v>0.2350226044654846</v>
       </c>
       <c r="FK8" t="n">
-        <v>0.00193546456284821</v>
+        <v>0.04885956272482872</v>
       </c>
       <c r="FL8" t="n">
-        <v>0.003737025894224644</v>
+        <v>0.08648737519979477</v>
       </c>
       <c r="FM8" t="n">
-        <v>0.0001994384219869971</v>
+        <v>0.1164665445685387</v>
       </c>
       <c r="FN8" t="n">
-        <v>0.0004243833245709538</v>
+        <v>0.206154078245163</v>
       </c>
       <c r="FO8" t="n">
-        <v>0.003067226149141788</v>
+        <v>0.06351542472839355</v>
       </c>
       <c r="FP8" t="n">
-        <v>0.00244303303770721</v>
+        <v>0.1455784440040588</v>
       </c>
       <c r="FQ8" t="n">
-        <v>0.007912472821772099</v>
+        <v>0.1390949934720993</v>
       </c>
       <c r="FR8" t="n">
-        <v>0.001841203309595585</v>
+        <v>0.1517931520938873</v>
       </c>
       <c r="FS8" t="n">
-        <v>0.00198679231107235</v>
+        <v>0.1771549582481384</v>
       </c>
       <c r="FT8" t="n">
-        <v>0.0009541825274936855</v>
+        <v>0.03910411149263382</v>
       </c>
       <c r="FU8" t="n">
-        <v>0.005316657945513725</v>
+        <v>0.04663728922605515</v>
       </c>
       <c r="FV8" t="n">
-        <v>0.003853647271171212</v>
+        <v>0.06537521630525589</v>
       </c>
       <c r="FW8" t="n">
-        <v>0.003888336475938559</v>
+        <v>0.007928380742669106</v>
       </c>
       <c r="FX8" t="n">
-        <v>0.001526491483673453</v>
+        <v>0.01653161458671093</v>
       </c>
       <c r="FY8" t="n">
-        <v>0.005586768500506878</v>
+        <v>0.1069903969764709</v>
       </c>
       <c r="FZ8" t="n">
-        <v>0.001550095272250473</v>
+        <v>0.01434619538486004</v>
       </c>
       <c r="GA8" t="n">
-        <v>0.0009570543770678341</v>
+        <v>0.05512500181794167</v>
       </c>
       <c r="GB8" t="n">
-        <v>0.0004366700304672122</v>
+        <v>0.002288510324433446</v>
       </c>
       <c r="GC8" t="n">
-        <v>0.002484039170667529</v>
+        <v>0.146410197019577</v>
       </c>
       <c r="GD8" t="n">
-        <v>0.004613971337676048</v>
+        <v>0.09527080506086349</v>
       </c>
       <c r="GE8" t="n">
-        <v>0.01175856031477451</v>
+        <v>0.08422908186912537</v>
       </c>
       <c r="GF8" t="n">
-        <v>0.001510399044491351</v>
+        <v>0.06092357635498047</v>
       </c>
       <c r="GG8" t="n">
-        <v>0.001917184796184301</v>
+        <v>0.03433852270245552</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2.701530320337042e-06</v>
+        <v>0.1844857484102249</v>
       </c>
       <c r="B9" t="n">
-        <v>0.003750470466911793</v>
+        <v>0.3455001711845398</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0005409479490481317</v>
+        <v>0.0001799208112061024</v>
       </c>
       <c r="D9" t="n">
-        <v>0.002281212946400046</v>
+        <v>0.7448345422744751</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0009111390681937337</v>
+        <v>0.1163220852613449</v>
       </c>
       <c r="F9" t="n">
-        <v>4.298991552786902e-05</v>
+        <v>0.220333606004715</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0003873544628731906</v>
+        <v>0.2337401062250137</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0004742139135487378</v>
+        <v>0.1322558522224426</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0001862666103988886</v>
+        <v>0.06101580709218979</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0002756290487013757</v>
+        <v>0.2416317164897919</v>
       </c>
       <c r="K9" t="n">
-        <v>0.003027528757229447</v>
+        <v>0.3281297087669373</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0001649795158300549</v>
+        <v>0.1508018523454666</v>
       </c>
       <c r="M9" t="n">
-        <v>0.002128837164491415</v>
+        <v>1.002925157546997</v>
       </c>
       <c r="N9" t="n">
-        <v>0.001123161753639579</v>
+        <v>0.174579992890358</v>
       </c>
       <c r="O9" t="n">
-        <v>0.000337215926265344</v>
+        <v>0.1604174822568893</v>
       </c>
       <c r="P9" t="n">
-        <v>0.0002509881160221994</v>
+        <v>0.1860964298248291</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.0003187533875461668</v>
+        <v>0.02876772917807102</v>
       </c>
       <c r="R9" t="n">
-        <v>0.0001163092092610896</v>
+        <v>0.1503960341215134</v>
       </c>
       <c r="S9" t="n">
-        <v>0.000149908839375712</v>
+        <v>0.05647887662053108</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0006641588406637311</v>
+        <v>0.006146833300590515</v>
       </c>
       <c r="U9" t="n">
-        <v>3.174964149366133e-05</v>
+        <v>0.07830028980970383</v>
       </c>
       <c r="V9" t="n">
-        <v>0.0001202370622195303</v>
+        <v>0.03320441395044327</v>
       </c>
       <c r="W9" t="n">
-        <v>0.0003659032809082419</v>
+        <v>0.1321171075105667</v>
       </c>
       <c r="X9" t="n">
-        <v>0.0003327080339659005</v>
+        <v>0.1593257337808609</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.000385740480851382</v>
+        <v>0.002300120890140533</v>
       </c>
       <c r="Z9" t="n">
-        <v>7.491777068935335e-05</v>
+        <v>0.009319020435214043</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.0002031333569902927</v>
+        <v>0.08498149365186691</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.0005500711849890649</v>
+        <v>0.07619535177946091</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.0007003794889897108</v>
+        <v>0.195107489824295</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.0001316413545282558</v>
+        <v>0.0981726348400116</v>
       </c>
       <c r="AE9" t="n">
-        <v>5.847310603712685e-05</v>
+        <v>0.01762961596250534</v>
       </c>
       <c r="AF9" t="n">
-        <v>6.979412864893675e-05</v>
+        <v>0.1011679619550705</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.0001825483050197363</v>
+        <v>0.05710699409246445</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.0001758928847266361</v>
+        <v>0.05986900627613068</v>
       </c>
       <c r="AI9" t="n">
-        <v>9.881059668259695e-05</v>
+        <v>0.1158563494682312</v>
       </c>
       <c r="AJ9" t="n">
-        <v>2.02763476409018e-06</v>
+        <v>0.1260808259248734</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.0001437236642232165</v>
+        <v>0.05782971903681755</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.0004445418599061668</v>
+        <v>0.03471573442220688</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.847401472332422e-05</v>
+        <v>0.1386618614196777</v>
       </c>
       <c r="AN9" t="n">
-        <v>7.142481626942754e-05</v>
+        <v>0.09641696512699127</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.0002104712912114337</v>
+        <v>0.1099878400564194</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.0003877775452565402</v>
+        <v>0.176154762506485</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.0002269084798172116</v>
+        <v>0.1222205385565758</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.000349438632838428</v>
+        <v>0.09763491898775101</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.0001216955861309543</v>
+        <v>0.01278072223067284</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.0003147754759993404</v>
+        <v>0.06442444026470184</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.00263484288007021</v>
+        <v>0.228849858045578</v>
       </c>
       <c r="AV9" t="n">
-        <v>9.19033627724275e-05</v>
+        <v>0.06097652390599251</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.0006309565505944192</v>
+        <v>0.4045725166797638</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.812235677789431e-05</v>
+        <v>0.3374350965023041</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.0002255997533211485</v>
+        <v>0.03246785327792168</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.0001364720810670406</v>
+        <v>0.01827606000006199</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.000131706619868055</v>
+        <v>0.1156829744577408</v>
       </c>
       <c r="BB9" t="n">
-        <v>6.648538692388684e-05</v>
+        <v>0.08233051747083664</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.0003117989399470389</v>
+        <v>0.1224964484572411</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.0007247740868479013</v>
+        <v>0.1272690296173096</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.0006611464777961373</v>
+        <v>0.04449665918946266</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.0004570257151499391</v>
+        <v>0.1114295423030853</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.001022514188662171</v>
+        <v>0.339298814535141</v>
       </c>
       <c r="BH9" t="n">
-        <v>4.389424429973587e-05</v>
+        <v>0.1524586975574493</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.0004873302823398262</v>
+        <v>0.0279700830578804</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.000314332137349993</v>
+        <v>0.2319627851247787</v>
       </c>
       <c r="BK9" t="n">
-        <v>8.182712190318853e-05</v>
+        <v>0.18437659740448</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.0005683651543222368</v>
+        <v>0.00571022555232048</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.0004792566760443151</v>
+        <v>0.1156209856271744</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.0003251738962717354</v>
+        <v>0.05341397225856781</v>
       </c>
       <c r="BO9" t="n">
-        <v>8.978921687230468e-05</v>
+        <v>0.1456785798072815</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.0004932816373184323</v>
+        <v>0.1654627025127411</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.0003000476281158626</v>
+        <v>0.03712497279047966</v>
       </c>
       <c r="BR9" t="n">
-        <v>2.848737494787201e-06</v>
+        <v>0.001969754695892334</v>
       </c>
       <c r="BS9" t="n">
-        <v>8.479255484417081e-05</v>
+        <v>0.08945190161466599</v>
       </c>
       <c r="BT9" t="n">
-        <v>0.0001811138936318457</v>
+        <v>0.0496399849653244</v>
       </c>
       <c r="BU9" t="n">
-        <v>0.0002019673702307045</v>
+        <v>0.06873819231987</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.001342743285931647</v>
+        <v>0.04419960081577301</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.0006123567000031471</v>
+        <v>0.05137598514556885</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.0002640394377522171</v>
+        <v>0.2647048830986023</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.0003193705924786627</v>
+        <v>0.1606719791889191</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.0002132038353011012</v>
+        <v>0.1431348025798798</v>
       </c>
       <c r="CA9" t="n">
-        <v>0.0001811857509892434</v>
+        <v>0.04823879897594452</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.0001100529116229154</v>
+        <v>0.001170718111097813</v>
       </c>
       <c r="CC9" t="n">
-        <v>9.508074435871094e-05</v>
+        <v>0.02971511706709862</v>
       </c>
       <c r="CD9" t="n">
-        <v>5.884251004317775e-05</v>
+        <v>0.0006780438125133514</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.0006673600873909891</v>
+        <v>0.05130685493350029</v>
       </c>
       <c r="CF9" t="n">
-        <v>0.0001407065865350887</v>
+        <v>0.002876222599297762</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.000217272958252579</v>
+        <v>0.2380649447441101</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.0001326463825535029</v>
+        <v>0.02598911896348</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.634824340930209e-05</v>
+        <v>0.003869172651320696</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0.0001287580525968224</v>
+        <v>0.00590790156275034</v>
       </c>
       <c r="CK9" t="n">
-        <v>4.270687713869847e-05</v>
+        <v>0.03712469339370728</v>
       </c>
       <c r="CL9" t="n">
-        <v>5.592465822701342e-05</v>
+        <v>0.01656125113368034</v>
       </c>
       <c r="CM9" t="n">
-        <v>0.0008400364313274622</v>
+        <v>0.001553848385810852</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.000517331063747406</v>
+        <v>0.1144568771123886</v>
       </c>
       <c r="CO9" t="n">
-        <v>5.329425039235502e-05</v>
+        <v>0.08777333050966263</v>
       </c>
       <c r="CP9" t="n">
-        <v>0.0007404111092910171</v>
+        <v>0.1226027756929398</v>
       </c>
       <c r="CQ9" t="n">
-        <v>0.0006584536749869585</v>
+        <v>0.1779380142688751</v>
       </c>
       <c r="CR9" t="n">
-        <v>0.0005568041815422475</v>
+        <v>0.05418143793940544</v>
       </c>
       <c r="CS9" t="n">
-        <v>0.0003463063621893525</v>
+        <v>0.0911913588643074</v>
       </c>
       <c r="CT9" t="n">
-        <v>0.0008537047542631626</v>
+        <v>0.1923501342535019</v>
       </c>
       <c r="CU9" t="n">
-        <v>0.0001074140309356153</v>
+        <v>0.1836604475975037</v>
       </c>
       <c r="CV9" t="n">
-        <v>6.210013089003041e-05</v>
+        <v>0.01031392998993397</v>
       </c>
       <c r="CW9" t="n">
-        <v>0.0005850633606314659</v>
+        <v>0.064974345266819</v>
       </c>
       <c r="CX9" t="n">
-        <v>0.0002336906472919509</v>
+        <v>0.005427791271358728</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.0003659126814454794</v>
+        <v>0.2520511448383331</v>
       </c>
       <c r="CZ9" t="n">
-        <v>0.0001521695521660149</v>
+        <v>0.01748615875840187</v>
       </c>
       <c r="DA9" t="n">
-        <v>5.321293792803772e-05</v>
+        <v>0.000600066501647234</v>
       </c>
       <c r="DB9" t="n">
-        <v>9.254295582650229e-05</v>
+        <v>0.01561172399669886</v>
       </c>
       <c r="DC9" t="n">
-        <v>5.446071372716688e-05</v>
+        <v>0.03722592070698738</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.098288289038464e-06</v>
+        <v>0.01949264481663704</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.0002882208791561425</v>
+        <v>0.1009828075766563</v>
       </c>
       <c r="DF9" t="n">
-        <v>0.0005337900365702808</v>
+        <v>0.02671647444367409</v>
       </c>
       <c r="DG9" t="n">
-        <v>0.00029367784736678</v>
+        <v>0.2101763635873795</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.0009065544581972063</v>
+        <v>0.1718212366104126</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.0002584594185464084</v>
+        <v>0.06900805979967117</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.359481732128188e-05</v>
+        <v>0.05607185512781143</v>
       </c>
       <c r="DK9" t="n">
-        <v>0.0002983066078741103</v>
+        <v>0.04720798507332802</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.0001348756049992517</v>
+        <v>0.3563043177127838</v>
       </c>
       <c r="DM9" t="n">
-        <v>0.0003104376955889165</v>
+        <v>0.04699737206101418</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.0001339468726655468</v>
+        <v>0.07147505134344101</v>
       </c>
       <c r="DO9" t="n">
-        <v>0.0003712250618264079</v>
+        <v>0.05127649009227753</v>
       </c>
       <c r="DP9" t="n">
-        <v>0.000120288270409219</v>
+        <v>0.07348155230283737</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0.000234140723478049</v>
+        <v>0.1098422482609749</v>
       </c>
       <c r="DR9" t="n">
-        <v>0.0004665761953219771</v>
+        <v>0.1794608980417252</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.0001422787754563615</v>
+        <v>0.2000090777873993</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.0001094178587663919</v>
+        <v>0.05485814809799194</v>
       </c>
       <c r="DU9" t="n">
-        <v>9.720106754684821e-05</v>
+        <v>0.04600352793931961</v>
       </c>
       <c r="DV9" t="n">
-        <v>3.835819370578974e-06</v>
+        <v>0.1976944953203201</v>
       </c>
       <c r="DW9" t="n">
-        <v>2.175321060349233e-05</v>
+        <v>0.07266196608543396</v>
       </c>
       <c r="DX9" t="n">
-        <v>0.0002698720782063901</v>
+        <v>0.02778111398220062</v>
       </c>
       <c r="DY9" t="n">
-        <v>0.0001637622044654563</v>
+        <v>0.1177834123373032</v>
       </c>
       <c r="DZ9" t="n">
-        <v>1.720942782412749e-05</v>
+        <v>0.05958949029445648</v>
       </c>
       <c r="EA9" t="n">
-        <v>0.000672332476824522</v>
+        <v>0.1251836717128754</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.0002353452291572466</v>
+        <v>0.002363160252571106</v>
       </c>
       <c r="EC9" t="n">
-        <v>0.0001064310636138543</v>
+        <v>0.02407462522387505</v>
       </c>
       <c r="ED9" t="n">
-        <v>3.665006079245359e-05</v>
+        <v>0.3645177185535431</v>
       </c>
       <c r="EE9" t="n">
-        <v>8.718045137356967e-06</v>
+        <v>0.08738596737384796</v>
       </c>
       <c r="EF9" t="n">
-        <v>1.325219636783004e-05</v>
+        <v>0.02869384735822678</v>
       </c>
       <c r="EG9" t="n">
-        <v>0.0005068461177870631</v>
+        <v>0.02984658256173134</v>
       </c>
       <c r="EH9" t="n">
-        <v>0.0001385636278428137</v>
+        <v>0.00387175171636045</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.0004685415478888899</v>
+        <v>0.2631192207336426</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.0003691467572934926</v>
+        <v>0.05170906707644463</v>
       </c>
       <c r="EK9" t="n">
-        <v>6.786976882722229e-06</v>
+        <v>0.05011226236820221</v>
       </c>
       <c r="EL9" t="n">
-        <v>0.0001776498829713091</v>
+        <v>0.003670774400234222</v>
       </c>
       <c r="EM9" t="n">
-        <v>4.443717261892743e-05</v>
+        <v>0.05928833782672882</v>
       </c>
       <c r="EN9" t="n">
-        <v>3.658308924059384e-05</v>
+        <v>0.01837090030312538</v>
       </c>
       <c r="EO9" t="n">
-        <v>0.0001740030711516738</v>
+        <v>0.03276670724153519</v>
       </c>
       <c r="EP9" t="n">
-        <v>0.0004591374308802187</v>
+        <v>0.0491010993719101</v>
       </c>
       <c r="EQ9" t="n">
-        <v>0.0004662075079977512</v>
+        <v>0.009208150207996368</v>
       </c>
       <c r="ER9" t="n">
-        <v>0.0003209033457096666</v>
+        <v>0.165404886007309</v>
       </c>
       <c r="ES9" t="n">
-        <v>0.0001981621608138084</v>
+        <v>0.07038868218660355</v>
       </c>
       <c r="ET9" t="n">
-        <v>4.296951738069765e-05</v>
+        <v>0.283304899930954</v>
       </c>
       <c r="EU9" t="n">
-        <v>0.0002441683609504253</v>
+        <v>0.101406566798687</v>
       </c>
       <c r="EV9" t="n">
-        <v>0.0001732237142277882</v>
+        <v>0.03171637654304504</v>
       </c>
       <c r="EW9" t="n">
-        <v>7.271675713127479e-05</v>
+        <v>0.1777814775705338</v>
       </c>
       <c r="EX9" t="n">
-        <v>6.440735887736082e-05</v>
+        <v>0.003428494557738304</v>
       </c>
       <c r="EY9" t="n">
-        <v>0.0006325456197373569</v>
+        <v>0.06857716292142868</v>
       </c>
       <c r="EZ9" t="n">
-        <v>0.0001308611826971173</v>
+        <v>0.01693859696388245</v>
       </c>
       <c r="FA9" t="n">
-        <v>0.0002906438312493265</v>
+        <v>0.2642261981964111</v>
       </c>
       <c r="FB9" t="n">
-        <v>0.0001029491832014173</v>
+        <v>0.01711414381861687</v>
       </c>
       <c r="FC9" t="n">
-        <v>0.0001255545066669583</v>
+        <v>0.01361815445125103</v>
       </c>
       <c r="FD9" t="n">
-        <v>0.0001411300181644037</v>
+        <v>0.01139178872108459</v>
       </c>
       <c r="FE9" t="n">
-        <v>6.078253500163555e-05</v>
+        <v>0.0634845644235611</v>
       </c>
       <c r="FF9" t="n">
-        <v>5.532414797926322e-05</v>
+        <v>0.02362219989299774</v>
       </c>
       <c r="FG9" t="n">
-        <v>6.721775571350008e-05</v>
+        <v>0.05888409167528152</v>
       </c>
       <c r="FH9" t="n">
-        <v>0.0001120715533033945</v>
+        <v>0.00492529571056366</v>
       </c>
       <c r="FI9" t="n">
-        <v>0.0002028353337664157</v>
+        <v>0.04632744193077087</v>
       </c>
       <c r="FJ9" t="n">
-        <v>0.0003232241433579475</v>
+        <v>0.07662586867809296</v>
       </c>
       <c r="FK9" t="n">
-        <v>0.0004318372521083802</v>
+        <v>0.0153272021561861</v>
       </c>
       <c r="FL9" t="n">
-        <v>0.0003692880272865295</v>
+        <v>0.006858086213469505</v>
       </c>
       <c r="FM9" t="n">
-        <v>0.0001166229485534132</v>
+        <v>0.03237396478652954</v>
       </c>
       <c r="FN9" t="n">
-        <v>3.488181391730905e-06</v>
+        <v>0.1594952791929245</v>
       </c>
       <c r="FO9" t="n">
-        <v>0.0002225003554485738</v>
+        <v>0.09758643060922623</v>
       </c>
       <c r="FP9" t="n">
-        <v>0.0002835536724887788</v>
+        <v>0.001313012093305588</v>
       </c>
       <c r="FQ9" t="n">
-        <v>0.0001109330332837999</v>
+        <v>0.1890219748020172</v>
       </c>
       <c r="FR9" t="n">
-        <v>0.0003763439599424601</v>
+        <v>0.09655115008354187</v>
       </c>
       <c r="FS9" t="n">
-        <v>3.842583828372881e-05</v>
+        <v>0.2346915006637573</v>
       </c>
       <c r="FT9" t="n">
-        <v>1.386093208566308e-05</v>
+        <v>0.1403679251670837</v>
       </c>
       <c r="FU9" t="n">
-        <v>8.288101525977254e-05</v>
+        <v>0.1492992043495178</v>
       </c>
       <c r="FV9" t="n">
-        <v>0.0001612588530406356</v>
+        <v>0.01324150711297989</v>
       </c>
       <c r="FW9" t="n">
-        <v>3.697583451867104e-05</v>
+        <v>0.1076967939734459</v>
       </c>
       <c r="FX9" t="n">
-        <v>0.0002630283124744892</v>
+        <v>0.07935995608568192</v>
       </c>
       <c r="FY9" t="n">
-        <v>0.0005154145183041692</v>
+        <v>0.0140242138877511</v>
       </c>
       <c r="FZ9" t="n">
-        <v>0.0001499297068221495</v>
+        <v>0.01653369702398777</v>
       </c>
       <c r="GA9" t="n">
-        <v>5.373440944822505e-05</v>
+        <v>0.1178174391388893</v>
       </c>
       <c r="GB9" t="n">
-        <v>4.025692760478705e-06</v>
+        <v>0.104880154132843</v>
       </c>
       <c r="GC9" t="n">
-        <v>1.415920269209892e-05</v>
+        <v>0.31805419921875</v>
       </c>
       <c r="GD9" t="n">
-        <v>0.0002659591846168041</v>
+        <v>0.06270250678062439</v>
       </c>
       <c r="GE9" t="n">
-        <v>0.0005989085766486824</v>
+        <v>0.2202067375183105</v>
       </c>
       <c r="GF9" t="n">
-        <v>9.414921805728227e-05</v>
+        <v>0.00624386640265584</v>
       </c>
       <c r="GG9" t="n">
-        <v>8.246633660746738e-05</v>
+        <v>0.05450581014156342</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.008437216281890869</v>
+        <v>0.9176161289215088</v>
       </c>
       <c r="B10" t="n">
-        <v>0.009141985327005386</v>
+        <v>0.5627721548080444</v>
       </c>
       <c r="C10" t="n">
-        <v>0.01240007020533085</v>
+        <v>0.5439300537109375</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0008906765142455697</v>
+        <v>0.3553816378116608</v>
       </c>
       <c r="E10" t="n">
-        <v>0.006329359486699104</v>
+        <v>0.5580406188964844</v>
       </c>
       <c r="F10" t="n">
-        <v>0.006566491443663836</v>
+        <v>0.4421645998954773</v>
       </c>
       <c r="G10" t="n">
-        <v>0.004992968868464231</v>
+        <v>0.4899338185787201</v>
       </c>
       <c r="H10" t="n">
-        <v>0.001286859391257167</v>
+        <v>0.1890369653701782</v>
       </c>
       <c r="I10" t="n">
-        <v>0.002342243678867817</v>
+        <v>0.08784706890583038</v>
       </c>
       <c r="J10" t="n">
-        <v>0.003761853091418743</v>
+        <v>1.030771732330322</v>
       </c>
       <c r="K10" t="n">
-        <v>0.003922780510038137</v>
+        <v>0.4515140652656555</v>
       </c>
       <c r="L10" t="n">
-        <v>0.008984596468508244</v>
+        <v>0.5020434260368347</v>
       </c>
       <c r="M10" t="n">
-        <v>0.006041712127625942</v>
+        <v>0.0800083726644516</v>
       </c>
       <c r="N10" t="n">
-        <v>0.01008831895887852</v>
+        <v>0.5169233083724976</v>
       </c>
       <c r="O10" t="n">
-        <v>0.001868219580501318</v>
+        <v>0.1392989158630371</v>
       </c>
       <c r="P10" t="n">
-        <v>0.002410115674138069</v>
+        <v>0.648308277130127</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.0004548549477476627</v>
+        <v>0.1864266693592072</v>
       </c>
       <c r="R10" t="n">
-        <v>0.005903958342969418</v>
+        <v>0.1205305755138397</v>
       </c>
       <c r="S10" t="n">
-        <v>0.003196145175024867</v>
+        <v>0.1673156023025513</v>
       </c>
       <c r="T10" t="n">
-        <v>0.005261320620775223</v>
+        <v>0.4646836817264557</v>
       </c>
       <c r="U10" t="n">
-        <v>0.006239109206944704</v>
+        <v>0.1801393628120422</v>
       </c>
       <c r="V10" t="n">
-        <v>0.00154496415052563</v>
+        <v>0.2298678159713745</v>
       </c>
       <c r="W10" t="n">
-        <v>0.0007433849386870861</v>
+        <v>0.2001078128814697</v>
       </c>
       <c r="X10" t="n">
-        <v>0.0006940951570868492</v>
+        <v>0.2312554270029068</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.0002670524118002504</v>
+        <v>0.1453913599252701</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.000866991002112627</v>
+        <v>0.02938230894505978</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.000419328804127872</v>
+        <v>0.1748998016119003</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.0004317776765674353</v>
+        <v>0.412751704454422</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.002141915960237384</v>
+        <v>0.3300447762012482</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.002944940235465765</v>
+        <v>0.1833132207393646</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.002809980884194374</v>
+        <v>0.1840967833995819</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.00138485583011061</v>
+        <v>0.1674806326627731</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.003151276148855686</v>
+        <v>0.2878358662128448</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.001049987855367362</v>
+        <v>0.2066541612148285</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.002274862956255674</v>
+        <v>0.06373004615306854</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.0009905549231916666</v>
+        <v>0.2275612652301788</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.001075311098247766</v>
+        <v>0.2240195423364639</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.006555069703608751</v>
+        <v>0.4966843128204346</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.0009824428707361221</v>
+        <v>0.2223968803882599</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.00179289816878736</v>
+        <v>0.2159780859947205</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.003497551195323467</v>
+        <v>0.3046824038028717</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.004408515524119139</v>
+        <v>0.1316975057125092</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.0009750779718160629</v>
+        <v>0.1697282344102859</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.001137201790697873</v>
+        <v>0.04470126330852509</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.001175852259621024</v>
+        <v>0.0664203017950058</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.006773593369871378</v>
+        <v>0.6424617767333984</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.0002230517566204071</v>
+        <v>0.4981670379638672</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.009786743670701981</v>
+        <v>0.1482011079788208</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.0008534894441254437</v>
+        <v>0.3419574201107025</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.006826454307883978</v>
+        <v>0.366057425737381</v>
       </c>
       <c r="AY10" t="n">
-        <v>6.753836350981146e-05</v>
+        <v>0.1101269200444221</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.004121274221688509</v>
+        <v>0.1320130228996277</v>
       </c>
       <c r="BA10" t="n">
-        <v>7.454364094883204e-06</v>
+        <v>0.2855557799339294</v>
       </c>
       <c r="BB10" t="n">
-        <v>0.006061933934688568</v>
+        <v>0.1489754021167755</v>
       </c>
       <c r="BC10" t="n">
-        <v>0.002516793319955468</v>
+        <v>0.02908166125416756</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.01246840693056583</v>
+        <v>0.2287835478782654</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.001105081522837281</v>
+        <v>0.08372700214385986</v>
       </c>
       <c r="BF10" t="n">
-        <v>0.005414539948105812</v>
+        <v>0.05512694269418716</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.005103392526507378</v>
+        <v>0.7477446794509888</v>
       </c>
       <c r="BH10" t="n">
-        <v>0.01221183314919472</v>
+        <v>0.02834085002541542</v>
       </c>
       <c r="BI10" t="n">
-        <v>0.002300280844792724</v>
+        <v>0.2815739214420319</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.006943571846932173</v>
+        <v>0.5995330810546875</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.00671191094443202</v>
+        <v>0.1483151763677597</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.0001267269253730774</v>
+        <v>0.0173763781785965</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.001612434629350901</v>
+        <v>0.2439541220664978</v>
       </c>
       <c r="BN10" t="n">
-        <v>0.00473300414159894</v>
+        <v>0.04974868893623352</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.005614698864519596</v>
+        <v>0.160723090171814</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.0008726034429855645</v>
+        <v>0.003435388207435608</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0.003802666440606117</v>
+        <v>0.01233752071857452</v>
       </c>
       <c r="BR10" t="n">
-        <v>0.001767846173606813</v>
+        <v>0.1745619624853134</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.002319548511877656</v>
+        <v>0.1342980563640594</v>
       </c>
       <c r="BT10" t="n">
-        <v>0.002003093017265201</v>
+        <v>0.1730589419603348</v>
       </c>
       <c r="BU10" t="n">
-        <v>0.002298418432474136</v>
+        <v>0.3406572639942169</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.002385822357609868</v>
+        <v>0.5867530107498169</v>
       </c>
       <c r="BW10" t="n">
-        <v>0.003721290966495872</v>
+        <v>0.07051383703947067</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.0008838206995278597</v>
+        <v>0.1857379227876663</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.004782663192600012</v>
+        <v>0.2648009955883026</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0.002574382349848747</v>
+        <v>0.1507199555635452</v>
       </c>
       <c r="CA10" t="n">
-        <v>7.457990432158113e-05</v>
+        <v>0.1470949947834015</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.003910247702151537</v>
+        <v>0.1207509934902191</v>
       </c>
       <c r="CC10" t="n">
-        <v>0.006735891569405794</v>
+        <v>0.1698217391967773</v>
       </c>
       <c r="CD10" t="n">
-        <v>0.0008892323239706457</v>
+        <v>0.1616125404834747</v>
       </c>
       <c r="CE10" t="n">
-        <v>0.000215260311961174</v>
+        <v>0.1451739072799683</v>
       </c>
       <c r="CF10" t="n">
-        <v>0.002146045211702585</v>
+        <v>0.08413296192884445</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.001860194839537144</v>
+        <v>0.02656448632478714</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.0003191833384335041</v>
+        <v>0.0249748956412077</v>
       </c>
       <c r="CI10" t="n">
-        <v>0.0002035727229667827</v>
+        <v>0.1929591000080109</v>
       </c>
       <c r="CJ10" t="n">
-        <v>0.001222747494466603</v>
+        <v>0.1048980355262756</v>
       </c>
       <c r="CK10" t="n">
-        <v>0.001505570020526648</v>
+        <v>0.01515821367502213</v>
       </c>
       <c r="CL10" t="n">
-        <v>0.000952015514485538</v>
+        <v>0.004281111061573029</v>
       </c>
       <c r="CM10" t="n">
-        <v>0.001231289003044367</v>
+        <v>0.05935093760490417</v>
       </c>
       <c r="CN10" t="n">
-        <v>0.0004069495480507612</v>
+        <v>0.364983081817627</v>
       </c>
       <c r="CO10" t="n">
-        <v>0.0001641842536628246</v>
+        <v>0.04355109483003616</v>
       </c>
       <c r="CP10" t="n">
-        <v>0.002374843927100301</v>
+        <v>0.07137924432754517</v>
       </c>
       <c r="CQ10" t="n">
-        <v>0.004363813903182745</v>
+        <v>0.07142087817192078</v>
       </c>
       <c r="CR10" t="n">
-        <v>0.0008566057658754289</v>
+        <v>0.1900106072425842</v>
       </c>
       <c r="CS10" t="n">
-        <v>0.003985555376857519</v>
+        <v>0.1607949733734131</v>
       </c>
       <c r="CT10" t="n">
-        <v>0.001336756977252662</v>
+        <v>0.3129377961158752</v>
       </c>
       <c r="CU10" t="n">
-        <v>0.002865440445020795</v>
+        <v>0.1508878469467163</v>
       </c>
       <c r="CV10" t="n">
-        <v>7.128872675821185e-05</v>
+        <v>0.2009453624486923</v>
       </c>
       <c r="CW10" t="n">
-        <v>0.001359528279863298</v>
+        <v>0.1314079463481903</v>
       </c>
       <c r="CX10" t="n">
-        <v>0.00207601860165596</v>
+        <v>0.09130062162876129</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.001631237799301744</v>
+        <v>0.01921059377491474</v>
       </c>
       <c r="CZ10" t="n">
-        <v>5.727639654651284e-05</v>
+        <v>0.06901368498802185</v>
       </c>
       <c r="DA10" t="n">
-        <v>0.0004031641292385757</v>
+        <v>0.226965993642807</v>
       </c>
       <c r="DB10" t="n">
-        <v>0.001003380515612662</v>
+        <v>0.1849947869777679</v>
       </c>
       <c r="DC10" t="n">
-        <v>0.0001554253394715488</v>
+        <v>0.03285348415374756</v>
       </c>
       <c r="DD10" t="n">
-        <v>0.0009123620111495256</v>
+        <v>0.04701118916273117</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.00154461560305208</v>
+        <v>0.236238956451416</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.000706113176420331</v>
+        <v>0.1116212457418442</v>
       </c>
       <c r="DG10" t="n">
-        <v>0.01366825960576534</v>
+        <v>0.3623282313346863</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.004965432919561863</v>
+        <v>0.4055542051792145</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.0007145840208977461</v>
+        <v>0.3939017653465271</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0.000112177076516673</v>
+        <v>1.038114428520203</v>
       </c>
       <c r="DK10" t="n">
-        <v>0.00101995887234807</v>
+        <v>0.01364731695502996</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.004983341787010431</v>
+        <v>0.1185098513960838</v>
       </c>
       <c r="DM10" t="n">
-        <v>0.003654823172837496</v>
+        <v>0.1247049868106842</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.0007050432031974196</v>
+        <v>0.2072484791278839</v>
       </c>
       <c r="DO10" t="n">
-        <v>0.00579542201012373</v>
+        <v>0.1911814212799072</v>
       </c>
       <c r="DP10" t="n">
-        <v>0.0008740301709622145</v>
+        <v>0.1793394982814789</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0.001527603017166257</v>
+        <v>0.01211816351860762</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.002251382917165756</v>
+        <v>0.1481408923864365</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.003318077186122537</v>
+        <v>0.02821656875312328</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.001001129159703851</v>
+        <v>0.119786761701107</v>
       </c>
       <c r="DU10" t="n">
-        <v>0.003952507860958576</v>
+        <v>0.2873867452144623</v>
       </c>
       <c r="DV10" t="n">
-        <v>0.006542331073433161</v>
+        <v>0.2665247321128845</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.0006217823829501867</v>
+        <v>0.1974790841341019</v>
       </c>
       <c r="DX10" t="n">
-        <v>9.174106526188552e-05</v>
+        <v>0.09142936766147614</v>
       </c>
       <c r="DY10" t="n">
-        <v>0.0005937861278653145</v>
+        <v>0.1333359479904175</v>
       </c>
       <c r="DZ10" t="n">
-        <v>0.0005822773673571646</v>
+        <v>0.2854967713356018</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.004393282812088728</v>
+        <v>0.01174171455204487</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.001409407122991979</v>
+        <v>0.5292929410934448</v>
       </c>
       <c r="EC10" t="n">
-        <v>0.0002748364058788866</v>
+        <v>0.1466000080108643</v>
       </c>
       <c r="ED10" t="n">
-        <v>0.003735971869900823</v>
+        <v>0.2568985819816589</v>
       </c>
       <c r="EE10" t="n">
-        <v>0.003527302760630846</v>
+        <v>0.04237215965986252</v>
       </c>
       <c r="EF10" t="n">
-        <v>0.0008613160462118685</v>
+        <v>0.08649059385061264</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.007610919885337353</v>
+        <v>0.04677623510360718</v>
       </c>
       <c r="EH10" t="n">
-        <v>0.006063283421099186</v>
+        <v>0.0001286454498767853</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.001743263565003872</v>
+        <v>0.04659284651279449</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.002102693542838097</v>
+        <v>0.1176000982522964</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.002261952264234424</v>
+        <v>0.1283350884914398</v>
       </c>
       <c r="EL10" t="n">
-        <v>0.002284405985847116</v>
+        <v>0.1558666974306107</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.0001429099938832223</v>
+        <v>0.07568134367465973</v>
       </c>
       <c r="EN10" t="n">
-        <v>0.003343382850289345</v>
+        <v>0.122812882065773</v>
       </c>
       <c r="EO10" t="n">
-        <v>0.002052535535767674</v>
+        <v>0.127238467335701</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.002923015970736742</v>
+        <v>0.1767620146274567</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0.001804685569368303</v>
+        <v>0.05105097964406013</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.0003124686772935092</v>
+        <v>0.03935998678207397</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.00637749582529068</v>
+        <v>0.3775260150432587</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.001018129289150238</v>
+        <v>0.04957373067736626</v>
       </c>
       <c r="EU10" t="n">
-        <v>0.0005709343822672963</v>
+        <v>0.2626919448375702</v>
       </c>
       <c r="EV10" t="n">
-        <v>0.002177352551370859</v>
+        <v>0.3789618909358978</v>
       </c>
       <c r="EW10" t="n">
-        <v>0.005990616045892239</v>
+        <v>0.1824617832899094</v>
       </c>
       <c r="EX10" t="n">
-        <v>0.0005559457931667566</v>
+        <v>0.1933790296316147</v>
       </c>
       <c r="EY10" t="n">
-        <v>2.585415495559573e-05</v>
+        <v>0.1995903551578522</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0.001822466496378183</v>
+        <v>0.09400184452533722</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.001537043950520456</v>
+        <v>0.05550168827176094</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.001002574455924332</v>
+        <v>0.01836094446480274</v>
       </c>
       <c r="FC10" t="n">
-        <v>0.001731146941892803</v>
+        <v>0.2015219926834106</v>
       </c>
       <c r="FD10" t="n">
-        <v>0.0008095414377748966</v>
+        <v>0.1390490680932999</v>
       </c>
       <c r="FE10" t="n">
-        <v>0.0009828918846324086</v>
+        <v>0.01173718553036451</v>
       </c>
       <c r="FF10" t="n">
-        <v>0.0002785743854474276</v>
+        <v>0.09197145700454712</v>
       </c>
       <c r="FG10" t="n">
-        <v>0.002720116171985865</v>
+        <v>0.5378227829933167</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.003995231818407774</v>
+        <v>0.04375430941581726</v>
       </c>
       <c r="FI10" t="n">
-        <v>0.0002514836378395557</v>
+        <v>0.2500249743461609</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.0009851726936176419</v>
+        <v>0.2100922912359238</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.002016727114096284</v>
+        <v>0.2377912700176239</v>
       </c>
       <c r="FL10" t="n">
-        <v>0.002992782508954406</v>
+        <v>0.02983900159597397</v>
       </c>
       <c r="FM10" t="n">
-        <v>0.0005680026370100677</v>
+        <v>0.00354047492146492</v>
       </c>
       <c r="FN10" t="n">
-        <v>0.00410342775285244</v>
+        <v>0.2502257823944092</v>
       </c>
       <c r="FO10" t="n">
-        <v>0.0007055505411699414</v>
+        <v>0.3065925538539886</v>
       </c>
       <c r="FP10" t="n">
-        <v>0.006702053360641003</v>
+        <v>0.3022147417068481</v>
       </c>
       <c r="FQ10" t="n">
-        <v>0.00145976385101676</v>
+        <v>0.4506806135177612</v>
       </c>
       <c r="FR10" t="n">
-        <v>0.00296325096860528</v>
+        <v>0.1377558410167694</v>
       </c>
       <c r="FS10" t="n">
-        <v>0.005689747165888548</v>
+        <v>0.6262380480766296</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.005208142101764679</v>
+        <v>0.03225244581699371</v>
       </c>
       <c r="FU10" t="n">
-        <v>0.002333753276616335</v>
+        <v>0.2825818657875061</v>
       </c>
       <c r="FV10" t="n">
-        <v>0.000848819559905678</v>
+        <v>0.03394356369972229</v>
       </c>
       <c r="FW10" t="n">
-        <v>0.00992355402559042</v>
+        <v>0.2466644495725632</v>
       </c>
       <c r="FX10" t="n">
-        <v>0.0001647444441914558</v>
+        <v>0.4362593591213226</v>
       </c>
       <c r="FY10" t="n">
-        <v>0.001094034407287836</v>
+        <v>0.04620429500937462</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.004508636426180601</v>
+        <v>0.3395557701587677</v>
       </c>
       <c r="GA10" t="n">
-        <v>0.003622629679739475</v>
+        <v>0.06948601454496384</v>
       </c>
       <c r="GB10" t="n">
-        <v>0.002437945455312729</v>
+        <v>0.1046041771769524</v>
       </c>
       <c r="GC10" t="n">
-        <v>0.0004611957992892712</v>
+        <v>0.16457200050354</v>
       </c>
       <c r="GD10" t="n">
-        <v>0.0007034558220766485</v>
+        <v>0.3384765684604645</v>
       </c>
       <c r="GE10" t="n">
-        <v>0.001265434897504747</v>
+        <v>0.1537623405456543</v>
       </c>
       <c r="GF10" t="n">
-        <v>0.002784025622531772</v>
+        <v>0.004861805588006973</v>
       </c>
       <c r="GG10" t="n">
-        <v>0.001997957238927484</v>
+        <v>0.002092327922582626</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.0003114817372988909</v>
+        <v>0.06145823746919632</v>
       </c>
       <c r="B11" t="n">
-        <v>0.006658436264842749</v>
+        <v>0.3202217221260071</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0004535325570032001</v>
+        <v>0.0006413012742996216</v>
       </c>
       <c r="D11" t="n">
-        <v>0.003507358022034168</v>
+        <v>0.03361215069890022</v>
       </c>
       <c r="E11" t="n">
-        <v>0.001076516346074641</v>
+        <v>0.02150263637304306</v>
       </c>
       <c r="F11" t="n">
-        <v>0.006619609892368317</v>
+        <v>0.1456758677959442</v>
       </c>
       <c r="G11" t="n">
-        <v>8.526994497515261e-05</v>
+        <v>0.005722234956920147</v>
       </c>
       <c r="H11" t="n">
-        <v>0.002861337503418326</v>
+        <v>0.05955558270215988</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0005798629717901349</v>
+        <v>0.0008707698434591293</v>
       </c>
       <c r="J11" t="n">
-        <v>0.00141509051900357</v>
+        <v>0.02779486030340195</v>
       </c>
       <c r="K11" t="n">
-        <v>0.006056691519916058</v>
+        <v>0.3939886093139648</v>
       </c>
       <c r="L11" t="n">
-        <v>7.259455742314458e-05</v>
+        <v>0.01193438097834587</v>
       </c>
       <c r="M11" t="n">
-        <v>0.002760220551863313</v>
+        <v>0.08184389024972916</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0006021721055731177</v>
+        <v>0.08355142176151276</v>
       </c>
       <c r="O11" t="n">
-        <v>0.006740001030266285</v>
+        <v>0.1497145742177963</v>
       </c>
       <c r="P11" t="n">
-        <v>4.201679257676005e-05</v>
+        <v>0.06629570573568344</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.001062426483258605</v>
+        <v>0.06243336573243141</v>
       </c>
       <c r="R11" t="n">
-        <v>0.0004449023981578648</v>
+        <v>0.02056038193404675</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0004191080224700272</v>
+        <v>0.02081060782074928</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0008661516476422548</v>
+        <v>0.04924702271819115</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0001888469705590978</v>
+        <v>0.01457915455102921</v>
       </c>
       <c r="V11" t="n">
-        <v>0.0004566608986351639</v>
+        <v>0.0755283534526825</v>
       </c>
       <c r="W11" t="n">
-        <v>7.08007428329438e-06</v>
+        <v>0.04634813591837883</v>
       </c>
       <c r="X11" t="n">
-        <v>0.0003191145369783044</v>
+        <v>0.03044063039124012</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.0006099293241277337</v>
+        <v>0.02645283378660679</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.0005630491650663316</v>
+        <v>0.09453301876783371</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.0003948401426896453</v>
+        <v>0.009911357425153255</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.0002053638454526663</v>
+        <v>0.03886353224515915</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.0008283147471956909</v>
+        <v>0.01628127880394459</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.0001397977612214163</v>
+        <v>0.01615998335182667</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.0002768428530544043</v>
+        <v>0.04953642934560776</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.0001181986881420016</v>
+        <v>0.1323411911725998</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.0004223895957693458</v>
+        <v>0.0407654196023941</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.0003723030677065253</v>
+        <v>0.01404135674238205</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.0008996143005788326</v>
+        <v>0.08836856484413147</v>
       </c>
       <c r="AJ11" t="n">
-        <v>2.182889147661626e-06</v>
+        <v>0.02113443240523338</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.0006738491356372833</v>
+        <v>0.01129102054983377</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.0009499705047346652</v>
+        <v>0.03761422261595726</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.0001024808443617076</v>
+        <v>0.02170602604746819</v>
       </c>
       <c r="AN11" t="n">
-        <v>0.0004034066223539412</v>
+        <v>0.04025540500879288</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.0005641539464704692</v>
+        <v>0.007161408662796021</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.001277035917155445</v>
+        <v>0.04118343070149422</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.0004387305816635489</v>
+        <v>0.04684861376881599</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.0004087536653969437</v>
+        <v>0.09942905604839325</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.0008141805883497</v>
+        <v>0.01812090910971165</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.0004910407587885857</v>
+        <v>0.02777431160211563</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.004209703765809536</v>
+        <v>0.3160750567913055</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.000315585290081799</v>
+        <v>0.007308651693165302</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.0004324584151618183</v>
+        <v>0.01052875071763992</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.0006008787313476205</v>
+        <v>0.09316030144691467</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.003374591236934066</v>
+        <v>0.1455608904361725</v>
       </c>
       <c r="AZ11" t="n">
-        <v>2.533868246246129e-05</v>
+        <v>0.005490773357450962</v>
       </c>
       <c r="BA11" t="n">
-        <v>0.001544948434457183</v>
+        <v>0.006257428787648678</v>
       </c>
       <c r="BB11" t="n">
-        <v>0.0005309036932885647</v>
+        <v>0.0151244355365634</v>
       </c>
       <c r="BC11" t="n">
-        <v>0.0005022604018449783</v>
+        <v>0.009725883603096008</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.001615376677364111</v>
+        <v>0.01325332187116146</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.002114982577040792</v>
+        <v>0.01784577965736389</v>
       </c>
       <c r="BF11" t="n">
-        <v>0.001117482781410217</v>
+        <v>0.04369992762804031</v>
       </c>
       <c r="BG11" t="n">
-        <v>0.002193171065300703</v>
+        <v>0.01844644732773304</v>
       </c>
       <c r="BH11" t="n">
-        <v>0.002600164618343115</v>
+        <v>0.01550036761909723</v>
       </c>
       <c r="BI11" t="n">
-        <v>6.820025737397373e-05</v>
+        <v>0.03551281243562698</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.0008321141940541565</v>
+        <v>0.04774045944213867</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.0002587902708910406</v>
+        <v>0.02751529961824417</v>
       </c>
       <c r="BL11" t="n">
-        <v>6.603637302760035e-05</v>
+        <v>0.03081636503338814</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.00134776090271771</v>
+        <v>0.0537685789167881</v>
       </c>
       <c r="BN11" t="n">
-        <v>0.0007208878523670137</v>
+        <v>0.01758814789354801</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.000948445638641715</v>
+        <v>0.02153600007295609</v>
       </c>
       <c r="BP11" t="n">
-        <v>5.813007010146976e-05</v>
+        <v>0.04701939597725868</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0.0002316391473868862</v>
+        <v>0.003566229715943336</v>
       </c>
       <c r="BR11" t="n">
-        <v>0.0005451000761240721</v>
+        <v>0.03996661677956581</v>
       </c>
       <c r="BS11" t="n">
-        <v>0.0005911311600357294</v>
+        <v>0.004606634378433228</v>
       </c>
       <c r="BT11" t="n">
-        <v>0.0003886200720444322</v>
+        <v>0.01792709529399872</v>
       </c>
       <c r="BU11" t="n">
-        <v>0.0002750351559370756</v>
+        <v>0.03018223494291306</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.002202808856964111</v>
+        <v>0.2107085287570953</v>
       </c>
       <c r="BW11" t="n">
-        <v>0.0006939124432392418</v>
+        <v>0.01589830219745636</v>
       </c>
       <c r="BX11" t="n">
-        <v>0.0003583972866181284</v>
+        <v>0.04082013666629791</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.466281537432224e-05</v>
+        <v>0.01713909208774567</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0.001566570019349456</v>
+        <v>0.08604370802640915</v>
       </c>
       <c r="CA11" t="n">
-        <v>0.0004448893014341593</v>
+        <v>0.03889510780572891</v>
       </c>
       <c r="CB11" t="n">
-        <v>0.0009225280955433846</v>
+        <v>0.06130062788724899</v>
       </c>
       <c r="CC11" t="n">
-        <v>0.0005252250703051686</v>
+        <v>0.00841470155864954</v>
       </c>
       <c r="CD11" t="n">
-        <v>5.078873800812289e-05</v>
+        <v>0.01600754261016846</v>
       </c>
       <c r="CE11" t="n">
-        <v>0.001170326373539865</v>
+        <v>0.09121908247470856</v>
       </c>
       <c r="CF11" t="n">
-        <v>0.0007144972332753241</v>
+        <v>0.001720180851407349</v>
       </c>
       <c r="CG11" t="n">
-        <v>0.0006167270475998521</v>
+        <v>0.02586543560028076</v>
       </c>
       <c r="CH11" t="n">
-        <v>0.0002028847520705312</v>
+        <v>0.008009626530110836</v>
       </c>
       <c r="CI11" t="n">
-        <v>0.0009982238989323378</v>
+        <v>0.05595778673887253</v>
       </c>
       <c r="CJ11" t="n">
-        <v>0.0004684135201387107</v>
+        <v>0.0207131989300251</v>
       </c>
       <c r="CK11" t="n">
-        <v>0.0003258638316765428</v>
+        <v>0.000758481677621603</v>
       </c>
       <c r="CL11" t="n">
-        <v>0.0003739614621736109</v>
+        <v>0.002562666311860085</v>
       </c>
       <c r="CM11" t="n">
-        <v>0.0008092976058833301</v>
+        <v>0.07653924077749252</v>
       </c>
       <c r="CN11" t="n">
-        <v>0.0005319399642758071</v>
+        <v>0.1871869415044785</v>
       </c>
       <c r="CO11" t="n">
-        <v>0.0002858251100406051</v>
+        <v>0.02638107351958752</v>
       </c>
       <c r="CP11" t="n">
-        <v>0.0009994995780289173</v>
+        <v>0.09847337007522583</v>
       </c>
       <c r="CQ11" t="n">
-        <v>9.879248682409525e-05</v>
+        <v>0.07665268331766129</v>
       </c>
       <c r="CR11" t="n">
-        <v>1.180582330562174e-05</v>
+        <v>0.09720834344625473</v>
       </c>
       <c r="CS11" t="n">
-        <v>0.001239823643118143</v>
+        <v>0.02782355062663555</v>
       </c>
       <c r="CT11" t="n">
-        <v>0.001117619452998042</v>
+        <v>0.03230845183134079</v>
       </c>
       <c r="CU11" t="n">
-        <v>0.0001461011124774814</v>
+        <v>0.003889618441462517</v>
       </c>
       <c r="CV11" t="n">
-        <v>0.0001165786161436699</v>
+        <v>0.001867678016424179</v>
       </c>
       <c r="CW11" t="n">
-        <v>0.0009324921411462128</v>
+        <v>0.08968023210763931</v>
       </c>
       <c r="CX11" t="n">
-        <v>0.0006842068978585303</v>
+        <v>0.001569802174344659</v>
       </c>
       <c r="CY11" t="n">
-        <v>0.000918727891985327</v>
+        <v>0.02555780857801437</v>
       </c>
       <c r="CZ11" t="n">
-        <v>0.0002414498158032075</v>
+        <v>0.00185046810656786</v>
       </c>
       <c r="DA11" t="n">
-        <v>0.001093625323846936</v>
+        <v>0.05033891648054123</v>
       </c>
       <c r="DB11" t="n">
-        <v>0.0003816436510533094</v>
+        <v>0.009150742553174496</v>
       </c>
       <c r="DC11" t="n">
-        <v>0.0006415589014068246</v>
+        <v>0.002288509393110871</v>
       </c>
       <c r="DD11" t="n">
-        <v>0.0002043932327069342</v>
+        <v>0.007014694157987833</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.0007982738898135722</v>
+        <v>0.003945108503103256</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.001009013969451189</v>
+        <v>0.05307693034410477</v>
       </c>
       <c r="DG11" t="n">
-        <v>8.009128214325756e-05</v>
+        <v>0.03480478748679161</v>
       </c>
       <c r="DH11" t="n">
-        <v>0.001819947501644492</v>
+        <v>0.03955398872494698</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.0004008375108242035</v>
+        <v>0.09006691724061966</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.783065428957343e-05</v>
+        <v>0.006893001962453127</v>
       </c>
       <c r="DK11" t="n">
-        <v>0.0006984989158809185</v>
+        <v>0.04308900982141495</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.00171434972435236</v>
+        <v>0.01553966011852026</v>
       </c>
       <c r="DM11" t="n">
-        <v>0.0007744120666757226</v>
+        <v>0.02306072972714901</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.0003431295626796782</v>
+        <v>0.03714937716722488</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.061853254213929e-07</v>
+        <v>0.06260360032320023</v>
       </c>
       <c r="DP11" t="n">
-        <v>0.0006233913591131568</v>
+        <v>0.02261167392134666</v>
       </c>
       <c r="DQ11" t="n">
-        <v>0.0005477418890222907</v>
+        <v>0.04481901228427887</v>
       </c>
       <c r="DR11" t="n">
-        <v>0.0005535581149160862</v>
+        <v>0.03390442952513695</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.0005328348488546908</v>
+        <v>0.02737316302955151</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.0002935680968221277</v>
+        <v>0.0222451239824295</v>
       </c>
       <c r="DU11" t="n">
-        <v>0.0001187552115879953</v>
+        <v>0.06825250387191772</v>
       </c>
       <c r="DV11" t="n">
-        <v>0.0007311482913792133</v>
+        <v>0.005166441667824984</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.0002807182027027011</v>
+        <v>0.0548558384180069</v>
       </c>
       <c r="DX11" t="n">
-        <v>0.000728256709408015</v>
+        <v>0.007213575765490532</v>
       </c>
       <c r="DY11" t="n">
-        <v>0.0007582674734294415</v>
+        <v>0.02988162450492382</v>
       </c>
       <c r="DZ11" t="n">
-        <v>0.0007969049620442092</v>
+        <v>0.005083741620182991</v>
       </c>
       <c r="EA11" t="n">
-        <v>2.615680568851531e-05</v>
+        <v>0.038465715944767</v>
       </c>
       <c r="EB11" t="n">
-        <v>0.0003153067955281585</v>
+        <v>0.03437337651848793</v>
       </c>
       <c r="EC11" t="n">
-        <v>5.583516758633777e-05</v>
+        <v>0.006426969543099403</v>
       </c>
       <c r="ED11" t="n">
-        <v>0.0002193223190261051</v>
+        <v>0.002362896222621202</v>
       </c>
       <c r="EE11" t="n">
-        <v>0.0003579104377422482</v>
+        <v>0.03255337476730347</v>
       </c>
       <c r="EF11" t="n">
-        <v>0.0004843944334425032</v>
+        <v>0.001354968175292015</v>
       </c>
       <c r="EG11" t="n">
-        <v>0.0009681166848167777</v>
+        <v>0.04696264490485191</v>
       </c>
       <c r="EH11" t="n">
-        <v>0.0005144341266714036</v>
+        <v>0.001730303280055523</v>
       </c>
       <c r="EI11" t="n">
-        <v>0.000232725142268464</v>
+        <v>0.009607816115021706</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.0001414053404005244</v>
+        <v>0.0296811331063509</v>
       </c>
       <c r="EK11" t="n">
-        <v>0.0008725596708245575</v>
+        <v>0.02768521383404732</v>
       </c>
       <c r="EL11" t="n">
-        <v>0.0007476137834601104</v>
+        <v>0.003023421624675393</v>
       </c>
       <c r="EM11" t="n">
-        <v>9.064193000085652e-05</v>
+        <v>0.03076888620853424</v>
       </c>
       <c r="EN11" t="n">
-        <v>2.396612399024889e-05</v>
+        <v>0.0008228829829022288</v>
       </c>
       <c r="EO11" t="n">
-        <v>0.0001002049684757367</v>
+        <v>0.005192727781832218</v>
       </c>
       <c r="EP11" t="n">
-        <v>0.0006054200930520892</v>
+        <v>0.03877490758895874</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0.0007978705689311028</v>
+        <v>0.01820701174438</v>
       </c>
       <c r="ER11" t="n">
-        <v>0.0009137779707089067</v>
+        <v>0.02098617516458035</v>
       </c>
       <c r="ES11" t="n">
-        <v>1.296787377214059e-05</v>
+        <v>0.02875027805566788</v>
       </c>
       <c r="ET11" t="n">
-        <v>0.0001145209098467603</v>
+        <v>0.01934432983398438</v>
       </c>
       <c r="EU11" t="n">
-        <v>0.0002713224675972015</v>
+        <v>0.01076300069689751</v>
       </c>
       <c r="EV11" t="n">
-        <v>0.001188090071082115</v>
+        <v>0.01277607958763838</v>
       </c>
       <c r="EW11" t="n">
-        <v>0.0001572722540004179</v>
+        <v>0.02345180325210094</v>
       </c>
       <c r="EX11" t="n">
-        <v>0.0001966955605894327</v>
+        <v>0.01251182518899441</v>
       </c>
       <c r="EY11" t="n">
-        <v>0.0009602885111235082</v>
+        <v>0.09860618412494659</v>
       </c>
       <c r="EZ11" t="n">
-        <v>0.0004872015269938856</v>
+        <v>0.0002141980221495032</v>
       </c>
       <c r="FA11" t="n">
-        <v>0.0006036548875272274</v>
+        <v>0.02350703440606594</v>
       </c>
       <c r="FB11" t="n">
-        <v>0.0001901990326587111</v>
+        <v>0.00703210337087512</v>
       </c>
       <c r="FC11" t="n">
-        <v>0.001023171003907919</v>
+        <v>0.05215026438236237</v>
       </c>
       <c r="FD11" t="n">
-        <v>0.0006125814979895949</v>
+        <v>0.02884798124432564</v>
       </c>
       <c r="FE11" t="n">
-        <v>0.0003582475474104285</v>
+        <v>0.007192651741206646</v>
       </c>
       <c r="FF11" t="n">
-        <v>0.0005003382684662938</v>
+        <v>0.01010273769497871</v>
       </c>
       <c r="FG11" t="n">
-        <v>0.0001921674993354827</v>
+        <v>0.02493668720126152</v>
       </c>
       <c r="FH11" t="n">
-        <v>5.843374310643412e-05</v>
+        <v>0.08775503188371658</v>
       </c>
       <c r="FI11" t="n">
-        <v>0.0007140941452234983</v>
+        <v>0.005310613662004471</v>
       </c>
       <c r="FJ11" t="n">
-        <v>0.001517805736511946</v>
+        <v>0.05770097672939301</v>
       </c>
       <c r="FK11" t="n">
-        <v>1.092387537937611e-05</v>
+        <v>0.03806358575820923</v>
       </c>
       <c r="FL11" t="n">
-        <v>0.001044298987835646</v>
+        <v>0.03571634739637375</v>
       </c>
       <c r="FM11" t="n">
-        <v>7.795785495545715e-05</v>
+        <v>0.02825726941227913</v>
       </c>
       <c r="FN11" t="n">
-        <v>0.0002355283359065652</v>
+        <v>0.09376775473356247</v>
       </c>
       <c r="FO11" t="n">
-        <v>0.0003357436507940292</v>
+        <v>0.002149784937500954</v>
       </c>
       <c r="FP11" t="n">
-        <v>0.0002953223302029073</v>
+        <v>0.0115104066208005</v>
       </c>
       <c r="FQ11" t="n">
-        <v>0.001011263928376138</v>
+        <v>0.0905030369758606</v>
       </c>
       <c r="FR11" t="n">
-        <v>0.0003387775795999914</v>
+        <v>0.01280024275183678</v>
       </c>
       <c r="FS11" t="n">
-        <v>0.0006724866107106209</v>
+        <v>0.1482583731412888</v>
       </c>
       <c r="FT11" t="n">
-        <v>0.001354722306132317</v>
+        <v>0.02159739285707474</v>
       </c>
       <c r="FU11" t="n">
-        <v>0.0009234948083758354</v>
+        <v>0.05316375195980072</v>
       </c>
       <c r="FV11" t="n">
-        <v>0.0002064991858787835</v>
+        <v>0.05292977020144463</v>
       </c>
       <c r="FW11" t="n">
-        <v>0.0001268176129087806</v>
+        <v>0.03677647560834885</v>
       </c>
       <c r="FX11" t="n">
-        <v>0.0003058339934796095</v>
+        <v>0.01328461803495884</v>
       </c>
       <c r="FY11" t="n">
-        <v>0.001293698791414499</v>
+        <v>0.0637253075838089</v>
       </c>
       <c r="FZ11" t="n">
-        <v>0.0003554490976966918</v>
+        <v>0.04746187850832939</v>
       </c>
       <c r="GA11" t="n">
-        <v>0.0002392134047113359</v>
+        <v>0.02837266959249973</v>
       </c>
       <c r="GB11" t="n">
-        <v>4.115397314308211e-05</v>
+        <v>0.01852216199040413</v>
       </c>
       <c r="GC11" t="n">
-        <v>0.0005332290893420577</v>
+        <v>0.02436326071619987</v>
       </c>
       <c r="GD11" t="n">
-        <v>0.001300150179304183</v>
+        <v>0.003298565279692411</v>
       </c>
       <c r="GE11" t="n">
-        <v>0.00242910860106349</v>
+        <v>0.05579503998160362</v>
       </c>
       <c r="GF11" t="n">
-        <v>0.0005419501103460789</v>
+        <v>0.009666349738836288</v>
       </c>
       <c r="GG11" t="n">
-        <v>0.0006779886316508055</v>
+        <v>0.04799161106348038</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.01144947670400143</v>
+        <v>0.1811333000659943</v>
       </c>
       <c r="B12" t="n">
-        <v>0.1504969447851181</v>
+        <v>0.1496536135673523</v>
       </c>
       <c r="C12" t="n">
-        <v>0.01532062515616417</v>
+        <v>0.05678666010499001</v>
       </c>
       <c r="D12" t="n">
-        <v>0.08022808283567429</v>
+        <v>0.6174843311309814</v>
       </c>
       <c r="E12" t="n">
-        <v>0.009256216697394848</v>
+        <v>0.08377513289451599</v>
       </c>
       <c r="F12" t="n">
-        <v>0.002556848805397749</v>
+        <v>0.2117529362440109</v>
       </c>
       <c r="G12" t="n">
-        <v>0.004522554576396942</v>
+        <v>0.2600199580192566</v>
       </c>
       <c r="H12" t="n">
-        <v>0.006742778234183788</v>
+        <v>0.139152318239212</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0151921147480607</v>
+        <v>0.04985537379980087</v>
       </c>
       <c r="J12" t="n">
-        <v>0.003764954395592213</v>
+        <v>0.2162473052740097</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1245111748576164</v>
+        <v>0.1059699282050133</v>
       </c>
       <c r="L12" t="n">
-        <v>0.002913932781666517</v>
+        <v>0.06436717510223389</v>
       </c>
       <c r="M12" t="n">
-        <v>0.08188043534755707</v>
+        <v>0.7965757846832275</v>
       </c>
       <c r="N12" t="n">
-        <v>0.03398919850587845</v>
+        <v>0.1045681908726692</v>
       </c>
       <c r="O12" t="n">
-        <v>0.002478230511769652</v>
+        <v>0.2202310264110565</v>
       </c>
       <c r="P12" t="n">
-        <v>0.006012355908751488</v>
+        <v>0.23857182264328</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.01468757819384336</v>
+        <v>0.03069514222443104</v>
       </c>
       <c r="R12" t="n">
-        <v>0.002638009609654546</v>
+        <v>0.1493622362613678</v>
       </c>
       <c r="S12" t="n">
-        <v>0.01014641020447016</v>
+        <v>0.004659573547542095</v>
       </c>
       <c r="T12" t="n">
-        <v>0.02531856298446655</v>
+        <v>0.04185522347688675</v>
       </c>
       <c r="U12" t="n">
-        <v>0.01642926409840584</v>
+        <v>0.04856795817613602</v>
       </c>
       <c r="V12" t="n">
-        <v>0.002674577059224248</v>
+        <v>0.03938476741313934</v>
       </c>
       <c r="W12" t="n">
-        <v>0.01990109123289585</v>
+        <v>0.1033170893788338</v>
       </c>
       <c r="X12" t="n">
-        <v>0.01923577487468719</v>
+        <v>0.1192190125584602</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.01522575598210096</v>
+        <v>0.007596805691719055</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.005501623265445232</v>
+        <v>0.03704418987035751</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.003026867983862758</v>
+        <v>0.00828228984028101</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.02585436031222343</v>
+        <v>0.005127698183059692</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.03472211584448814</v>
+        <v>0.003103539347648621</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.005253628827631474</v>
+        <v>0.06772290170192719</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.007632804103195667</v>
+        <v>0.07000711560249329</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.0008505875011906028</v>
+        <v>0.04897252470254898</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.001763288863003254</v>
+        <v>0.1516605764627457</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.001969275996088982</v>
+        <v>0.08110459893941879</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.0022533203009516</v>
+        <v>0.05441036075353622</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.002111888723447919</v>
+        <v>0.1257470548152924</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.006453018635511398</v>
+        <v>0.0685243159532547</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.007041017524898052</v>
+        <v>0.05527345836162567</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.005214375909417868</v>
+        <v>0.01932340860366821</v>
       </c>
       <c r="AN12" t="n">
-        <v>0.006987066939473152</v>
+        <v>0.07174637913703918</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.0192532129585743</v>
+        <v>0.04493723064661026</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.01875159703195095</v>
+        <v>0.1204714849591255</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.01202760729938745</v>
+        <v>0.09529004991054535</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.009602842852473259</v>
+        <v>0.04632605984807014</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.00173129967879504</v>
+        <v>0.02216958813369274</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.01229660026729107</v>
+        <v>0.1582396775484085</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.1054676845669746</v>
+        <v>0.1865897923707962</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.007515748962759972</v>
+        <v>0.04841962456703186</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.02985446527600288</v>
+        <v>0.2584138810634613</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.001259103417396545</v>
+        <v>0.2069101333618164</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.009920964017510414</v>
+        <v>0.117300808429718</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.01673180796205997</v>
+        <v>0.02721378579735756</v>
       </c>
       <c r="BA12" t="n">
-        <v>0.005780902691185474</v>
+        <v>0.004735084250569344</v>
       </c>
       <c r="BB12" t="n">
-        <v>0.01495716907083988</v>
+        <v>0.1073021441698074</v>
       </c>
       <c r="BC12" t="n">
-        <v>0.02232211641967297</v>
+        <v>0.02451028674840927</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.03791588172316551</v>
+        <v>0.07252173125743866</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.03203603997826576</v>
+        <v>0.03817278891801834</v>
       </c>
       <c r="BF12" t="n">
-        <v>0.0121734831482172</v>
+        <v>0.05886107310652733</v>
       </c>
       <c r="BG12" t="n">
-        <v>0.01476960722357035</v>
+        <v>0.1241683140397072</v>
       </c>
       <c r="BH12" t="n">
-        <v>0.02123440429568291</v>
+        <v>0.04405032843351364</v>
       </c>
       <c r="BI12" t="n">
-        <v>0.0168388020247221</v>
+        <v>0.09827110171318054</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.008081729523837566</v>
+        <v>0.06073273345828056</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.003714036662131548</v>
+        <v>0.09136214852333069</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.03049065545201302</v>
+        <v>0.004227085970342159</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.03865319117903709</v>
+        <v>0.06997855007648468</v>
       </c>
       <c r="BN12" t="n">
-        <v>0.02377462387084961</v>
+        <v>0.05893788859248161</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.001405722228810191</v>
+        <v>0.09936736524105072</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.03274954110383987</v>
+        <v>0.02436107397079468</v>
       </c>
       <c r="BQ12" t="n">
-        <v>0.01728870160877705</v>
+        <v>0.07177576422691345</v>
       </c>
       <c r="BR12" t="n">
-        <v>0.01727994903922081</v>
+        <v>0.06607574969530106</v>
       </c>
       <c r="BS12" t="n">
-        <v>0.006805109791457653</v>
+        <v>0.01852377317845821</v>
       </c>
       <c r="BT12" t="n">
-        <v>0.005791764240711927</v>
+        <v>0.005207660607993603</v>
       </c>
       <c r="BU12" t="n">
-        <v>0.01048655807971954</v>
+        <v>0.1108431741595268</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.05577325448393822</v>
+        <v>0.07494883239269257</v>
       </c>
       <c r="BW12" t="n">
-        <v>0.01880676113069057</v>
+        <v>0.01877911016345024</v>
       </c>
       <c r="BX12" t="n">
-        <v>0.01106781233102083</v>
+        <v>0.2057988345623016</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.0251929797232151</v>
+        <v>0.06805078685283661</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0.02230413816869259</v>
+        <v>0.1052138358354568</v>
       </c>
       <c r="CA12" t="n">
-        <v>0.001822424936108291</v>
+        <v>0.03382345288991928</v>
       </c>
       <c r="CB12" t="n">
-        <v>0.008250247687101364</v>
+        <v>0.03506297618150711</v>
       </c>
       <c r="CC12" t="n">
-        <v>0.0001540616503916681</v>
+        <v>0.01633626967668533</v>
       </c>
       <c r="CD12" t="n">
-        <v>0.0008689132519066334</v>
+        <v>0.08310224860906601</v>
       </c>
       <c r="CE12" t="n">
-        <v>0.02381194196641445</v>
+        <v>0.03703340888023376</v>
       </c>
       <c r="CF12" t="n">
-        <v>0.003986414056271315</v>
+        <v>0.05107644945383072</v>
       </c>
       <c r="CG12" t="n">
-        <v>0.006069791037589312</v>
+        <v>0.1855428814888</v>
       </c>
       <c r="CH12" t="n">
-        <v>0.006809944752603769</v>
+        <v>0.004988550208508968</v>
       </c>
       <c r="CI12" t="n">
-        <v>0.0009058307623490691</v>
+        <v>0.003145229071378708</v>
       </c>
       <c r="CJ12" t="n">
-        <v>0.004922123625874519</v>
+        <v>0.0005744015797972679</v>
       </c>
       <c r="CK12" t="n">
-        <v>0.001895082998089492</v>
+        <v>0.06002247333526611</v>
       </c>
       <c r="CL12" t="n">
-        <v>0.001177533878944814</v>
+        <v>0.00581222353503108</v>
       </c>
       <c r="CM12" t="n">
-        <v>0.03557520732283592</v>
+        <v>0.1823757141828537</v>
       </c>
       <c r="CN12" t="n">
-        <v>0.03242071345448494</v>
+        <v>0.06030258536338806</v>
       </c>
       <c r="CO12" t="n">
-        <v>0.002466131467372179</v>
+        <v>0.09657636284828186</v>
       </c>
       <c r="CP12" t="n">
-        <v>0.03231442347168922</v>
+        <v>0.209512859582901</v>
       </c>
       <c r="CQ12" t="n">
-        <v>0.04504749923944473</v>
+        <v>0.0871378481388092</v>
       </c>
       <c r="CR12" t="n">
-        <v>0.00781142245978117</v>
+        <v>0.1142269223928452</v>
       </c>
       <c r="CS12" t="n">
-        <v>0.00105154444463551</v>
+        <v>0.06905172020196915</v>
       </c>
       <c r="CT12" t="n">
-        <v>0.02949480153620243</v>
+        <v>0.05874791741371155</v>
       </c>
       <c r="CU12" t="n">
-        <v>0.003597133327275515</v>
+        <v>0.04690729454159737</v>
       </c>
       <c r="CV12" t="n">
-        <v>0.004369407426565886</v>
+        <v>0.09092114865779877</v>
       </c>
       <c r="CW12" t="n">
-        <v>0.02263648249208927</v>
+        <v>0.027196254581213</v>
       </c>
       <c r="CX12" t="n">
-        <v>0.009965988807380199</v>
+        <v>0.05601563304662704</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.01155843399465084</v>
+        <v>0.2049306333065033</v>
       </c>
       <c r="CZ12" t="n">
-        <v>0.01065077167004347</v>
+        <v>0.01201850920915604</v>
       </c>
       <c r="DA12" t="n">
-        <v>0.003059071255847812</v>
+        <v>0.006909763906151056</v>
       </c>
       <c r="DB12" t="n">
-        <v>0.001789073925465345</v>
+        <v>0.003983517177402973</v>
       </c>
       <c r="DC12" t="n">
-        <v>0.0004577640793286264</v>
+        <v>0.04239349812269211</v>
       </c>
       <c r="DD12" t="n">
-        <v>0.002185155171900988</v>
+        <v>0.01013489253818989</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.01891420409083366</v>
+        <v>0.111284039914608</v>
       </c>
       <c r="DF12" t="n">
-        <v>0.02196467109024525</v>
+        <v>0.005713492631912231</v>
       </c>
       <c r="DG12" t="n">
-        <v>0.01092184241861105</v>
+        <v>0.05831889808177948</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.04150235652923584</v>
+        <v>0.1383374631404877</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.00495636323466897</v>
+        <v>0.05241734534502029</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0.007385888136923313</v>
+        <v>0.1112240329384804</v>
       </c>
       <c r="DK12" t="n">
-        <v>0.001526889624074101</v>
+        <v>0.06299981474876404</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.01158357504755259</v>
+        <v>0.2553099691867828</v>
       </c>
       <c r="DM12" t="n">
-        <v>0.009550459682941437</v>
+        <v>0.06142653152346611</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.009300252422690392</v>
+        <v>0.04526251554489136</v>
       </c>
       <c r="DO12" t="n">
-        <v>0.01782942190766335</v>
+        <v>0.05780815333127975</v>
       </c>
       <c r="DP12" t="n">
-        <v>0.01131340209394693</v>
+        <v>0.004728100262582302</v>
       </c>
       <c r="DQ12" t="n">
-        <v>0.01894110441207886</v>
+        <v>0.04363394528627396</v>
       </c>
       <c r="DR12" t="n">
-        <v>0.02394521981477737</v>
+        <v>0.03618455305695534</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.0008676936849951744</v>
+        <v>0.1486674845218658</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.006735903210937977</v>
+        <v>0.07277598232030869</v>
       </c>
       <c r="DU12" t="n">
-        <v>0.008271541446447372</v>
+        <v>0.009152131155133247</v>
       </c>
       <c r="DV12" t="n">
-        <v>0.004292871337383986</v>
+        <v>0.1758115589618683</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.007223584223538637</v>
+        <v>0.02218698523938656</v>
       </c>
       <c r="DX12" t="n">
-        <v>0.03300395980477333</v>
+        <v>0.005352684296667576</v>
       </c>
       <c r="DY12" t="n">
-        <v>0.007858187891542912</v>
+        <v>0.1133003830909729</v>
       </c>
       <c r="DZ12" t="n">
-        <v>0.009687222540378571</v>
+        <v>0.03092117793858051</v>
       </c>
       <c r="EA12" t="n">
-        <v>0.03125056624412537</v>
+        <v>0.1412013322114944</v>
       </c>
       <c r="EB12" t="n">
-        <v>0.01571883261203766</v>
+        <v>0.1118414551019669</v>
       </c>
       <c r="EC12" t="n">
-        <v>0.009735610336065292</v>
+        <v>0.09207610040903091</v>
       </c>
       <c r="ED12" t="n">
-        <v>0.004753687418997288</v>
+        <v>0.1194376572966576</v>
       </c>
       <c r="EE12" t="n">
-        <v>0.003764999797567725</v>
+        <v>0.106552816927433</v>
       </c>
       <c r="EF12" t="n">
-        <v>0.009736058302223682</v>
+        <v>0.09330160170793533</v>
       </c>
       <c r="EG12" t="n">
-        <v>0.01000753417611122</v>
+        <v>0.02525142207741737</v>
       </c>
       <c r="EH12" t="n">
-        <v>0.005074639804661274</v>
+        <v>0.008785651996731758</v>
       </c>
       <c r="EI12" t="n">
-        <v>0.01966767944395542</v>
+        <v>0.1812045574188232</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.01491064205765724</v>
+        <v>0.02699785307049751</v>
       </c>
       <c r="EK12" t="n">
-        <v>0.004877352155745029</v>
+        <v>0.01065285503864288</v>
       </c>
       <c r="EL12" t="n">
-        <v>0.001361922477371991</v>
+        <v>0.001031333580613136</v>
       </c>
       <c r="EM12" t="n">
-        <v>0.0001467458787374198</v>
+        <v>0.05008487403392792</v>
       </c>
       <c r="EN12" t="n">
-        <v>0.0022678067907691</v>
+        <v>0.01476939208805561</v>
       </c>
       <c r="EO12" t="n">
-        <v>0.007327340543270111</v>
+        <v>0.08405813574790955</v>
       </c>
       <c r="EP12" t="n">
-        <v>0.02132338471710682</v>
+        <v>0.04787444323301315</v>
       </c>
       <c r="EQ12" t="n">
-        <v>0.01069468352943659</v>
+        <v>0.0620432160794735</v>
       </c>
       <c r="ER12" t="n">
-        <v>0.00311377621255815</v>
+        <v>0.2103483378887177</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.008723657578229904</v>
+        <v>0.008814949542284012</v>
       </c>
       <c r="ET12" t="n">
-        <v>0.004914251156151295</v>
+        <v>0.1107987686991692</v>
       </c>
       <c r="EU12" t="n">
-        <v>0.0003933779080398381</v>
+        <v>0.1106803417205811</v>
       </c>
       <c r="EV12" t="n">
-        <v>0.004381287842988968</v>
+        <v>0.01661375537514687</v>
       </c>
       <c r="EW12" t="n">
-        <v>0.003476555459201336</v>
+        <v>0.1963166296482086</v>
       </c>
       <c r="EX12" t="n">
-        <v>0.003074720967561007</v>
+        <v>0.09857181459665298</v>
       </c>
       <c r="EY12" t="n">
-        <v>0.02304818667471409</v>
+        <v>0.04639706015586853</v>
       </c>
       <c r="EZ12" t="n">
-        <v>0.003446137998253107</v>
+        <v>0.02777375094592571</v>
       </c>
       <c r="FA12" t="n">
-        <v>0.007586832158267498</v>
+        <v>0.2136104553937912</v>
       </c>
       <c r="FB12" t="n">
-        <v>0.003838331904262304</v>
+        <v>0.004175685346126556</v>
       </c>
       <c r="FC12" t="n">
-        <v>0.007521479856222868</v>
+        <v>0.03368250280618668</v>
       </c>
       <c r="FD12" t="n">
-        <v>0.0009033542592078447</v>
+        <v>0.02600077167153358</v>
       </c>
       <c r="FE12" t="n">
-        <v>0.0009504257468506694</v>
+        <v>0.05277691781520844</v>
       </c>
       <c r="FF12" t="n">
-        <v>0.001243531238287687</v>
+        <v>0.01027313806116581</v>
       </c>
       <c r="FG12" t="n">
-        <v>0.005146809387952089</v>
+        <v>0.002658051438629627</v>
       </c>
       <c r="FH12" t="n">
-        <v>0.02320501580834389</v>
+        <v>0.05992402136325836</v>
       </c>
       <c r="FI12" t="n">
-        <v>0.004607267677783966</v>
+        <v>0.07403561472892761</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0.009811265394091606</v>
+        <v>0.08250634372234344</v>
       </c>
       <c r="FK12" t="n">
-        <v>0.02095891162753105</v>
+        <v>0.138165757060051</v>
       </c>
       <c r="FL12" t="n">
-        <v>0.01570451445877552</v>
+        <v>0.07357224822044373</v>
       </c>
       <c r="FM12" t="n">
-        <v>0.02047693729400635</v>
+        <v>0.07236328721046448</v>
       </c>
       <c r="FN12" t="n">
-        <v>0.003660818794742227</v>
+        <v>0.001030969433486462</v>
       </c>
       <c r="FO12" t="n">
-        <v>0.0008282696362584829</v>
+        <v>0.02078267931938171</v>
       </c>
       <c r="FP12" t="n">
-        <v>0.004871371202170849</v>
+        <v>0.0138578750193119</v>
       </c>
       <c r="FQ12" t="n">
-        <v>0.009876130148768425</v>
+        <v>0.01263052318245173</v>
       </c>
       <c r="FR12" t="n">
-        <v>0.001393770799040794</v>
+        <v>0.02305980026721954</v>
       </c>
       <c r="FS12" t="n">
-        <v>0.0084037184715271</v>
+        <v>0.0764019787311554</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.02245535142719746</v>
+        <v>0.1337447613477707</v>
       </c>
       <c r="FU12" t="n">
-        <v>0.01189312431961298</v>
+        <v>0.04757626727223396</v>
       </c>
       <c r="FV12" t="n">
-        <v>0.009118018671870232</v>
+        <v>0.02352592535316944</v>
       </c>
       <c r="FW12" t="n">
-        <v>0.001686592469923198</v>
+        <v>0.2441994845867157</v>
       </c>
       <c r="FX12" t="n">
-        <v>0.004579117055982351</v>
+        <v>0.03107025288045406</v>
       </c>
       <c r="FY12" t="n">
-        <v>0.01948091760277748</v>
+        <v>0.05340957641601562</v>
       </c>
       <c r="FZ12" t="n">
-        <v>0.01414039172232151</v>
+        <v>0.03755331784486771</v>
       </c>
       <c r="GA12" t="n">
-        <v>0.005443787202239037</v>
+        <v>0.08528095483779907</v>
       </c>
       <c r="GB12" t="n">
-        <v>0.009608067572116852</v>
+        <v>0.2149699628353119</v>
       </c>
       <c r="GC12" t="n">
-        <v>0.007898533716797829</v>
+        <v>0.02794866822659969</v>
       </c>
       <c r="GD12" t="n">
-        <v>0.02519179508090019</v>
+        <v>0.04527047649025917</v>
       </c>
       <c r="GE12" t="n">
-        <v>0.005560021381825209</v>
+        <v>0.1727551519870758</v>
       </c>
       <c r="GF12" t="n">
-        <v>0.004353761672973633</v>
+        <v>0.04111867770552635</v>
       </c>
       <c r="GG12" t="n">
-        <v>0.001065847114659846</v>
+        <v>0.1398035734891891</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.01292691007256508</v>
+        <v>0.100840762257576</v>
       </c>
       <c r="B13" t="n">
-        <v>0.0004180208779871464</v>
+        <v>0.0151666384190321</v>
       </c>
       <c r="C13" t="n">
-        <v>0.002862116787582636</v>
+        <v>0.07198204845190048</v>
       </c>
       <c r="D13" t="n">
-        <v>0.007362076081335545</v>
+        <v>0.251144677400589</v>
       </c>
       <c r="E13" t="n">
-        <v>0.002399749821051955</v>
+        <v>0.09706130623817444</v>
       </c>
       <c r="F13" t="n">
-        <v>0.002834990154951811</v>
+        <v>0.01604400016367435</v>
       </c>
       <c r="G13" t="n">
-        <v>0.001827792031690478</v>
+        <v>0.06854280829429626</v>
       </c>
       <c r="H13" t="n">
-        <v>0.001120012835599482</v>
+        <v>0.0457073338329792</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0003884859324898571</v>
+        <v>0.02497638203203678</v>
       </c>
       <c r="J13" t="n">
-        <v>0.01130351237952709</v>
+        <v>0.06569123268127441</v>
       </c>
       <c r="K13" t="n">
-        <v>0.001227352535352111</v>
+        <v>0.04559941217303276</v>
       </c>
       <c r="L13" t="n">
-        <v>0.003550241002812982</v>
+        <v>0.07073540985584259</v>
       </c>
       <c r="M13" t="n">
-        <v>0.002917520934715867</v>
+        <v>0.3228094875812531</v>
       </c>
       <c r="N13" t="n">
-        <v>0.003241354133933783</v>
+        <v>0.02703339606523514</v>
       </c>
       <c r="O13" t="n">
-        <v>0.0005691564292646945</v>
+        <v>0.01713456213474274</v>
       </c>
       <c r="P13" t="n">
-        <v>0.0003517331788316369</v>
+        <v>0.04931986331939697</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.001591695356182754</v>
+        <v>0.04586197063326836</v>
       </c>
       <c r="R13" t="n">
-        <v>0.0008881108369678259</v>
+        <v>0.02858448959887028</v>
       </c>
       <c r="S13" t="n">
-        <v>0.001816441072151065</v>
+        <v>0.01475918758660555</v>
       </c>
       <c r="T13" t="n">
-        <v>0.002677228301763535</v>
+        <v>0.001452478114515543</v>
       </c>
       <c r="U13" t="n">
-        <v>0.001218819990754128</v>
+        <v>0.02057532221078873</v>
       </c>
       <c r="V13" t="n">
-        <v>0.0003081221657339483</v>
+        <v>0.03590669855475426</v>
       </c>
       <c r="W13" t="n">
-        <v>0.0007946976111270487</v>
+        <v>0.0410681739449501</v>
       </c>
       <c r="X13" t="n">
-        <v>0.0003769437316805124</v>
+        <v>0.1230463311076164</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.0003452260280027986</v>
+        <v>0.005817334167659283</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.002193327993154526</v>
+        <v>0.01562420092523098</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.0005050029722042382</v>
+        <v>0.00040457583963871</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.001406053081154823</v>
+        <v>0.004412742331624031</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.002732509979978204</v>
+        <v>0.01381818298250437</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.0005173551617190242</v>
+        <v>0.009243716485798359</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.0007182052358984947</v>
+        <v>0.03620470687747002</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.001094578532502055</v>
+        <v>0.1323256194591522</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.0008068624883890152</v>
+        <v>0.08898551017045975</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.0006220145151019096</v>
+        <v>0.03609536588191986</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.001130228396505117</v>
+        <v>0.05847083032131195</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.0007596216746605933</v>
+        <v>0.07008940726518631</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.001884884666651487</v>
+        <v>0.008079195395112038</v>
       </c>
       <c r="AL13" t="n">
-        <v>4.978018114343286e-05</v>
+        <v>0.02618653140962124</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.0005821776576340199</v>
+        <v>0.04795032367110252</v>
       </c>
       <c r="AN13" t="n">
-        <v>0.001325310091488063</v>
+        <v>0.09011363238096237</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.001605858677066863</v>
+        <v>0.03619356453418732</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.0005991435027681291</v>
+        <v>0.021987060084939</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.001474799122661352</v>
+        <v>0.07614615559577942</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.00156008277554065</v>
+        <v>0.01853047125041485</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.0006756687071174383</v>
+        <v>0.008950009010732174</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.008258676156401634</v>
+        <v>0.05123451352119446</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.00248586037196219</v>
+        <v>0.009333760477602482</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.003129234304651618</v>
+        <v>0.04318716377019882</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.00421185651794076</v>
+        <v>0.209179162979126</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.003098843386396766</v>
+        <v>0.03748282045125961</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.0004474915331229568</v>
+        <v>0.02895892225205898</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.0007040596683509648</v>
+        <v>0.05497097223997116</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.002999742049723864</v>
+        <v>0.02677156776189804</v>
       </c>
       <c r="BB13" t="n">
-        <v>0.0009903620230033994</v>
+        <v>0.0621509775519371</v>
       </c>
       <c r="BC13" t="n">
-        <v>0.005068816710263491</v>
+        <v>0.1013926044106483</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.006305650807917118</v>
+        <v>0.02670030668377876</v>
       </c>
       <c r="BE13" t="n">
-        <v>0.0006298352964222431</v>
+        <v>0.008789800107479095</v>
       </c>
       <c r="BF13" t="n">
-        <v>0.0004053547454532236</v>
+        <v>0.1074426025152206</v>
       </c>
       <c r="BG13" t="n">
-        <v>0.001810517045669258</v>
+        <v>0.125936895608902</v>
       </c>
       <c r="BH13" t="n">
-        <v>0.0002857029321603477</v>
+        <v>0.04889269545674324</v>
       </c>
       <c r="BI13" t="n">
-        <v>0.0007254082011058927</v>
+        <v>0.07304991036653519</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.002997897565364838</v>
+        <v>0.06361442059278488</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.001957024680450559</v>
+        <v>0.08474977314472198</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.0007021577330306172</v>
+        <v>0.01217123307287693</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.002961451187729836</v>
+        <v>0.05647748336195946</v>
       </c>
       <c r="BN13" t="n">
-        <v>0.0006006755866110325</v>
+        <v>0.03216759115457535</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.0005914706271141768</v>
+        <v>0.01082152128219604</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.0006493596592918038</v>
+        <v>0.0472034215927124</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.001025033532641828</v>
+        <v>0.007166972383856773</v>
       </c>
       <c r="BR13" t="n">
-        <v>0.001200031489133835</v>
+        <v>0.00426264014095068</v>
       </c>
       <c r="BS13" t="n">
-        <v>0.000461847463157028</v>
+        <v>0.01007615868002176</v>
       </c>
       <c r="BT13" t="n">
-        <v>0.000992167042568326</v>
+        <v>0.01403993740677834</v>
       </c>
       <c r="BU13" t="n">
-        <v>0.003613394452258945</v>
+        <v>0.03265393525362015</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.000132269284222275</v>
+        <v>0.04804912209510803</v>
       </c>
       <c r="BW13" t="n">
-        <v>0.001278395648114383</v>
+        <v>0.01785417459905148</v>
       </c>
       <c r="BX13" t="n">
-        <v>0.001913816086016595</v>
+        <v>0.183757483959198</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.897654146887362e-05</v>
+        <v>0.03445382043719292</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0.0004753763787448406</v>
+        <v>0.07198045402765274</v>
       </c>
       <c r="CA13" t="n">
-        <v>0.0005725665832869709</v>
+        <v>0.02753196470439434</v>
       </c>
       <c r="CB13" t="n">
-        <v>0.002160971518605947</v>
+        <v>0.03190767765045166</v>
       </c>
       <c r="CC13" t="n">
-        <v>0.0003853810485452414</v>
+        <v>0.03502542898058891</v>
       </c>
       <c r="CD13" t="n">
-        <v>0.00248588272370398</v>
+        <v>0.02812284603714943</v>
       </c>
       <c r="CE13" t="n">
-        <v>0.001938404166139662</v>
+        <v>0.01094299368560314</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.176250563934445e-05</v>
+        <v>0.01108701061457396</v>
       </c>
       <c r="CG13" t="n">
-        <v>0.0006551035912707448</v>
+        <v>0.0837831124663353</v>
       </c>
       <c r="CH13" t="n">
-        <v>7.106202247086912e-05</v>
+        <v>0.01403652876615524</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.001653965329751372</v>
+        <v>0.03567197918891907</v>
       </c>
       <c r="CJ13" t="n">
-        <v>2.277674502693117e-05</v>
+        <v>0.001629607053473592</v>
       </c>
       <c r="CK13" t="n">
-        <v>0.001497746212407947</v>
+        <v>0.02052387222647667</v>
       </c>
       <c r="CL13" t="n">
-        <v>0.0002613777760416269</v>
+        <v>0.02214399352669716</v>
       </c>
       <c r="CM13" t="n">
-        <v>0.003057763678953052</v>
+        <v>0.005613558460026979</v>
       </c>
       <c r="CN13" t="n">
-        <v>0.0009112437255680561</v>
+        <v>0.04647530242800713</v>
       </c>
       <c r="CO13" t="n">
-        <v>0.0001260069839190692</v>
+        <v>0.04184519127011299</v>
       </c>
       <c r="CP13" t="n">
-        <v>0.00260441261343658</v>
+        <v>0.1098596006631851</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.003485241439193487</v>
+        <v>0.1041636765003204</v>
       </c>
       <c r="CR13" t="n">
-        <v>0.001055261236615479</v>
+        <v>0.001282870303839445</v>
       </c>
       <c r="CS13" t="n">
-        <v>0.002714712871238589</v>
+        <v>0.004255473613739014</v>
       </c>
       <c r="CT13" t="n">
-        <v>0.00455891527235508</v>
+        <v>0.06155258417129517</v>
       </c>
       <c r="CU13" t="n">
-        <v>0.001227900153025985</v>
+        <v>0.08621398359537125</v>
       </c>
       <c r="CV13" t="n">
-        <v>0.001853640307672322</v>
+        <v>0.02561936527490616</v>
       </c>
       <c r="CW13" t="n">
-        <v>0.002266607247292995</v>
+        <v>0.01095244195312262</v>
       </c>
       <c r="CX13" t="n">
-        <v>0.0001881208445411175</v>
+        <v>0.00572283798828721</v>
       </c>
       <c r="CY13" t="n">
-        <v>0.0008150889188982546</v>
+        <v>0.08629859983921051</v>
       </c>
       <c r="CZ13" t="n">
-        <v>0.0001820807810872793</v>
+        <v>0.01191258989274502</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.001208147616125643</v>
+        <v>0.03209013119339943</v>
       </c>
       <c r="DB13" t="n">
-        <v>0.0002305073576280847</v>
+        <v>0.01065408624708652</v>
       </c>
       <c r="DC13" t="n">
-        <v>0.001139800995588303</v>
+        <v>0.01876675151288509</v>
       </c>
       <c r="DD13" t="n">
-        <v>0.0002199375012423843</v>
+        <v>0.009275693446397781</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.001370095531456172</v>
+        <v>0.01785507425665855</v>
       </c>
       <c r="DF13" t="n">
-        <v>0.002103178994730115</v>
+        <v>0.006357574369758368</v>
       </c>
       <c r="DG13" t="n">
-        <v>0.003397133434191346</v>
+        <v>0.02037714421749115</v>
       </c>
       <c r="DH13" t="n">
-        <v>0.004208615515381098</v>
+        <v>0.08798171579837799</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.0003550623077899218</v>
+        <v>0.01130337826907635</v>
       </c>
       <c r="DJ13" t="n">
-        <v>0.0007622501580044627</v>
+        <v>0.02687604166567326</v>
       </c>
       <c r="DK13" t="n">
-        <v>0.001122379559092224</v>
+        <v>0.04368864372372627</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.005156245548278093</v>
+        <v>0.1885580122470856</v>
       </c>
       <c r="DM13" t="n">
-        <v>0.0009838638361543417</v>
+        <v>0.03431321680545807</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.0009865659521892667</v>
+        <v>0.03839465230703354</v>
       </c>
       <c r="DO13" t="n">
-        <v>0.0001554213813506067</v>
+        <v>0.02766633778810501</v>
       </c>
       <c r="DP13" t="n">
-        <v>0.0009294521296396852</v>
+        <v>0.06846661865711212</v>
       </c>
       <c r="DQ13" t="n">
-        <v>0.001139191910624504</v>
+        <v>0.02986890263855457</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.002687808126211166</v>
+        <v>0.004913751035928726</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.001033661770634353</v>
+        <v>0.02124631032347679</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.0009472073870711029</v>
+        <v>0.001454384997487068</v>
       </c>
       <c r="DU13" t="n">
-        <v>0.0006547231459990144</v>
+        <v>0.01043127477169037</v>
       </c>
       <c r="DV13" t="n">
-        <v>0.001548318541608751</v>
+        <v>0.1011760905385017</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.002472800435498357</v>
+        <v>0.02022356726229191</v>
       </c>
       <c r="DX13" t="n">
-        <v>0.002005136106163263</v>
+        <v>0.01185871101915836</v>
       </c>
       <c r="DY13" t="n">
-        <v>0.0004303607274778187</v>
+        <v>0.09701115638017654</v>
       </c>
       <c r="DZ13" t="n">
-        <v>0.001107284100726247</v>
+        <v>0.008519597351551056</v>
       </c>
       <c r="EA13" t="n">
-        <v>0.001432852819561958</v>
+        <v>0.02991703152656555</v>
       </c>
       <c r="EB13" t="n">
-        <v>0.000807143107522279</v>
+        <v>0.005096187815070152</v>
       </c>
       <c r="EC13" t="n">
-        <v>0.000346888235071674</v>
+        <v>0.0319930836558342</v>
       </c>
       <c r="ED13" t="n">
-        <v>0.0002735382004175335</v>
+        <v>0.1287418901920319</v>
       </c>
       <c r="EE13" t="n">
-        <v>0.0007587160798721015</v>
+        <v>0.09726651757955551</v>
       </c>
       <c r="EF13" t="n">
-        <v>0.002397233387455344</v>
+        <v>0.04413637518882751</v>
       </c>
       <c r="EG13" t="n">
-        <v>0.002818581648170948</v>
+        <v>0.00716126523911953</v>
       </c>
       <c r="EH13" t="n">
-        <v>0.001416440238244832</v>
+        <v>0.01312356721609831</v>
       </c>
       <c r="EI13" t="n">
-        <v>0.002845393493771553</v>
+        <v>0.08202148973941803</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.002858795924112201</v>
+        <v>0.02110827341675758</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.0006854126113466918</v>
+        <v>0.01212719269096851</v>
       </c>
       <c r="EL13" t="n">
-        <v>0.0001302534656133503</v>
+        <v>0.01336599420756102</v>
       </c>
       <c r="EM13" t="n">
-        <v>0.0002659970195963979</v>
+        <v>0.01799996942281723</v>
       </c>
       <c r="EN13" t="n">
-        <v>0.0003034308028873056</v>
+        <v>0.0240623950958252</v>
       </c>
       <c r="EO13" t="n">
-        <v>0.0001769959344528615</v>
+        <v>0.0107030626386404</v>
       </c>
       <c r="EP13" t="n">
-        <v>0.004187334794551134</v>
+        <v>0.01307740155607462</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0.0007617475930601358</v>
+        <v>0.001915041822940111</v>
       </c>
       <c r="ER13" t="n">
-        <v>0.0001857280440162867</v>
+        <v>0.08199990540742874</v>
       </c>
       <c r="ES13" t="n">
-        <v>0.0001266535255126655</v>
+        <v>0.001592203974723816</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.001695097773335874</v>
+        <v>0.07888582348823547</v>
       </c>
       <c r="EU13" t="n">
-        <v>0.001151488977484405</v>
+        <v>0.04383773729205132</v>
       </c>
       <c r="EV13" t="n">
-        <v>0.0004517208435572684</v>
+        <v>0.001844406127929688</v>
       </c>
       <c r="EW13" t="n">
-        <v>0.002430742373690009</v>
+        <v>0.04999250173568726</v>
       </c>
       <c r="EX13" t="n">
-        <v>0.002026869682595134</v>
+        <v>0.0248266439884901</v>
       </c>
       <c r="EY13" t="n">
-        <v>0.002234447747468948</v>
+        <v>0.0008983666775748134</v>
       </c>
       <c r="EZ13" t="n">
-        <v>0.0003643847885541618</v>
+        <v>0.01354518532752991</v>
       </c>
       <c r="FA13" t="n">
-        <v>0.000697948329616338</v>
+        <v>0.105293408036232</v>
       </c>
       <c r="FB13" t="n">
-        <v>0.000232199759921059</v>
+        <v>0.02049423940479755</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.001266607665456831</v>
+        <v>0.009237853810191154</v>
       </c>
       <c r="FD13" t="n">
-        <v>0.0002036074001807719</v>
+        <v>0.01075472310185432</v>
       </c>
       <c r="FE13" t="n">
-        <v>0.001292675035074353</v>
+        <v>0.02971537038683891</v>
       </c>
       <c r="FF13" t="n">
-        <v>0.0003224470419809222</v>
+        <v>0.001295056426897645</v>
       </c>
       <c r="FG13" t="n">
-        <v>0.0002224047784693539</v>
+        <v>0.01436541229486465</v>
       </c>
       <c r="FH13" t="n">
-        <v>0.003019727766513824</v>
+        <v>0.0170592162758112</v>
       </c>
       <c r="FI13" t="n">
-        <v>0.002856518374755979</v>
+        <v>0.03343511000275612</v>
       </c>
       <c r="FJ13" t="n">
-        <v>0.0005392585298977792</v>
+        <v>0.05503853037953377</v>
       </c>
       <c r="FK13" t="n">
-        <v>0.001071549020707607</v>
+        <v>0.0313577875494957</v>
       </c>
       <c r="FL13" t="n">
-        <v>0.002975477138534188</v>
+        <v>0.01627817936241627</v>
       </c>
       <c r="FM13" t="n">
-        <v>0.001542597776278853</v>
+        <v>0.007353421300649643</v>
       </c>
       <c r="FN13" t="n">
-        <v>0.0007457080064341426</v>
+        <v>0.04852857068181038</v>
       </c>
       <c r="FO13" t="n">
-        <v>0.0009784840513020754</v>
+        <v>0.01235370058566332</v>
       </c>
       <c r="FP13" t="n">
-        <v>0.001847392879426479</v>
+        <v>0.02711344137787819</v>
       </c>
       <c r="FQ13" t="n">
-        <v>0.001466055517084897</v>
+        <v>0.007056940346956253</v>
       </c>
       <c r="FR13" t="n">
-        <v>0.001995599130168557</v>
+        <v>0.002030108822509646</v>
       </c>
       <c r="FS13" t="n">
-        <v>0.002112566493451595</v>
+        <v>0.1093519181013107</v>
       </c>
       <c r="FT13" t="n">
-        <v>0.003231540089473128</v>
+        <v>0.008806583471596241</v>
       </c>
       <c r="FU13" t="n">
-        <v>0.002577532082796097</v>
+        <v>0.08861072361469269</v>
       </c>
       <c r="FV13" t="n">
-        <v>0.00162515789270401</v>
+        <v>0.0569847859442234</v>
       </c>
       <c r="FW13" t="n">
-        <v>0.0003836986725218594</v>
+        <v>0.01721657812595367</v>
       </c>
       <c r="FX13" t="n">
-        <v>0.0006566513911820948</v>
+        <v>0.08349159359931946</v>
       </c>
       <c r="FY13" t="n">
-        <v>0.001244069542735815</v>
+        <v>0.01011909078806639</v>
       </c>
       <c r="FZ13" t="n">
-        <v>1.518588396720588e-05</v>
+        <v>0.05085153877735138</v>
       </c>
       <c r="GA13" t="n">
-        <v>4.314634134061635e-05</v>
+        <v>0.006575193256139755</v>
       </c>
       <c r="GB13" t="n">
-        <v>0.0002055882068816572</v>
+        <v>0.1141682043671608</v>
       </c>
       <c r="GC13" t="n">
-        <v>0.001222529332153499</v>
+        <v>0.03135384246706963</v>
       </c>
       <c r="GD13" t="n">
-        <v>0.0001872236171038821</v>
+        <v>0.02462631091475487</v>
       </c>
       <c r="GE13" t="n">
-        <v>0.001043526572175324</v>
+        <v>0.08159235119819641</v>
       </c>
       <c r="GF13" t="n">
-        <v>0.0007106675184331834</v>
+        <v>0.005981302820146084</v>
       </c>
       <c r="GG13" t="n">
-        <v>0.00118364836089313</v>
+        <v>0.002190590370446444</v>
       </c>
     </row>
     <row r="14">
